--- a/numerical-workflows/v2/framework/经济/模块产销表/07_玩法_竞技场.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/07_玩法_竞技场.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="玩法产出" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="资源汇总" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="机器明细" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="玩法产出" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$128</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'玩法产出'!$A$3:$V$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'资源汇总'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'机器明细'!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'玩法产出'!$A$3:$W$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'资源汇总'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'机器明细'!$A$1:$M$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -226,8 +226,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_readable" displayName="T_readable" ref="A1:J128" headerRowCount="1">
-  <autoFilter ref="A1:J128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_readable" displayName="T_readable" ref="A1:J129" headerRowCount="1">
+  <autoFilter ref="A1:J129"/>
   <tableColumns count="10">
     <tableColumn id="1" name="系统"/>
     <tableColumn id="2" name="分组"/>
@@ -245,9 +245,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_play_output" displayName="T_play_output" ref="A3:V118" headerRowCount="1">
-  <autoFilter ref="A3:V118"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_play_output" displayName="T_play_output" ref="A3:W119" headerRowCount="1">
+  <autoFilter ref="A3:W119"/>
+  <tableColumns count="23">
     <tableColumn id="1" name="阶段/条件"/>
     <tableColumn id="2" name="奖励/产出类型"/>
     <tableColumn id="3" name="周期/限制"/>
@@ -257,27 +257,28 @@
     <tableColumn id="7" name="产出_竞技场代币"/>
     <tableColumn id="8" name="产出_特供装置·单体"/>
     <tableColumn id="9" name="产出_特供装置·范围"/>
-    <tableColumn id="10" name="产出_元能核心"/>
-    <tableColumn id="11" name="产出_高阶记录盘"/>
-    <tableColumn id="12" name="产出_未知笔记"/>
-    <tableColumn id="13" name="产出_熔晶"/>
-    <tableColumn id="14" name="产出_猎鹰金币"/>
-    <tableColumn id="15" name="产出_合淬喷剂"/>
-    <tableColumn id="16" name="产出_校准元件"/>
-    <tableColumn id="17" name="产出_钻石"/>
-    <tableColumn id="18" name="产出_B炮台"/>
-    <tableColumn id="19" name="产出价值(钻石)"/>
-    <tableColumn id="20" name="消耗价值(钻石)"/>
-    <tableColumn id="21" name="来源"/>
-    <tableColumn id="22" name="备注"/>
+    <tableColumn id="10" name="产出_熔晶"/>
+    <tableColumn id="11" name="产出_定轨组件"/>
+    <tableColumn id="12" name="产出_秘制炸鸡桶"/>
+    <tableColumn id="13" name="产出_高阶记录盘"/>
+    <tableColumn id="14" name="产出_未知笔记"/>
+    <tableColumn id="15" name="产出_猎鹰金币"/>
+    <tableColumn id="16" name="产出_收容凭证"/>
+    <tableColumn id="17" name="产出_校准元件"/>
+    <tableColumn id="18" name="产出_钻石"/>
+    <tableColumn id="19" name="产出_B炮台"/>
+    <tableColumn id="20" name="产出价值(钻石)"/>
+    <tableColumn id="21" name="消耗价值(钻石)"/>
+    <tableColumn id="22" name="来源"/>
+    <tableColumn id="23" name="备注"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_resources" displayName="T_resources" ref="A1:J21" headerRowCount="1">
-  <autoFilter ref="A1:J21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_resources" displayName="T_resources" ref="A1:J22" headerRowCount="1">
+  <autoFilter ref="A1:J22"/>
   <tableColumns count="10">
     <tableColumn id="1" name="资源分类"/>
     <tableColumn id="2" name="资源/道具"/>
@@ -295,8 +296,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_arena" displayName="T_arena" ref="A1:M139" headerRowCount="1">
-  <autoFilter ref="A1:M139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_arena" displayName="T_arena" ref="A1:M141" headerRowCount="1">
+  <autoFilter ref="A1:M141"/>
   <tableColumns count="13">
     <tableColumn id="1" name="分组"/>
     <tableColumn id="2" name="方向"/>
@@ -684,7 +685,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +695,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -715,7 +716,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>产出:87；引用:42；消耗:9</t>
+          <t>产出:88；引用:42；消耗:10</t>
         </is>
       </c>
     </row>
@@ -739,7 +740,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币(19) 合计x20197；钻石(2) 合计x11800；炮台升级小材料(28) 合计x5400；炮台升级小材料 合计x80；B炮台(96303) 合计x1；元能核心(105) 合计x1；合淬喷剂(13) 合计x10000；未知笔记(110) 合计x10；校准元件(28) 合计x120；熔晶(103) 合计x1；另4项</t>
+          <t>竞技场代币(19) 合计x20197；钻石(2) 合计x11800；炮台升级小材料(28) 合计x5400；炮台升级小材料 合计x80；B炮台(96303) 合计x1；定轨组件(31) 合计x1；收容凭证(107) 合计x1；未知笔记(110) 合计x10；校准元件(28) 合计x120；熔晶(103) 合计x1；另5项</t>
         </is>
       </c>
     </row>
@@ -751,7 +752,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>勇士勋章(19) 合计x1230</t>
+          <t>勇士勋章(19) 合计x3385</t>
         </is>
       </c>
     </row>
@@ -775,7 +776,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场 x74；正式:Arena/ArenaRank.xlsx x24；正式:Shop/ShopGoods.xlsx#Arena x18；正式:Arena/ArenaWinStreak.xlsx x9；正式:Arena/ArenaWinReward.xlsx x6；竞技场 x4；正式:Arena/ArenaRankReward.xlsx x3</t>
+          <t>配置页-竞技场 x74；正式:Arena/ArenaRank.xlsx x24；正式:Shop/ShopGoods.xlsx#Arena x20；正式:Arena/ArenaWinStreak.xlsx x9；正式:Arena/ArenaWinReward.xlsx x6；竞技场 x4；正式:Arena/ArenaRankReward.xlsx x3</t>
         </is>
       </c>
     </row>
@@ -820,7 +821,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
@@ -852,7 +853,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -926,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2411,7 +2412,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥5胜</t>
+          <t>赛季累胜≥3胜</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
@@ -2451,7 +2452,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>赛季累胜≥6胜</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥9胜</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
@@ -2531,7 +2532,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥12胜</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
@@ -2571,7 +2572,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
@@ -2611,7 +2612,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥18胜</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
@@ -2651,7 +2652,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥24胜</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
@@ -2691,7 +2692,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥27胜</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr"/>
@@ -2731,7 +2732,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥60胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
@@ -2781,13 +2782,13 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x500</t>
+          <t>竞技场商店：勇士勋章(19) x1000</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:101</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:113</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -2797,7 +2798,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>兑换 特供装置·单体x1；正式 ShopGoods.Price=19,500</t>
+          <t>兑换 特供装置·单体x1；正式 ShopGoods.Price=19,1000</t>
         </is>
       </c>
     </row>
@@ -2829,13 +2830,13 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x500</t>
+          <t>竞技场商店：勇士勋章(19) x2000</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:102</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:114</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -2845,7 +2846,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>兑换 特供装置·范围x1；正式 ShopGoods.Price=19,500</t>
+          <t>兑换 特供装置·范围x1；正式 ShopGoods.Price=19,2000</t>
         </is>
       </c>
     </row>
@@ -2862,38 +2863,38 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109002｜ShopId 1109</t>
+          <t>ShopGoods 1109001｜ShopId 1109</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：元能核心(105) x1</t>
+          <t>竞技场商店：熔晶(103) x1</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x30</t>
+          <t>竞技场商店：勇士勋章(19) x150</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:95</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:106</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>商店兑换商品；商店兑换货币</t>
+          <t>商店兑换货币；商店兑换商品</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,30；兑换 元能核心x1</t>
+          <t>兑换 熔晶x1；正式 ShopGoods.Price=19,150</t>
         </is>
       </c>
     </row>
@@ -2910,28 +2911,28 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109004｜ShopId 1109</t>
+          <t>ShopGoods 1109010｜ShopId 1109</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：高阶记录盘(102) x10</t>
+          <t>竞技场商店：定轨组件(31) x1</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x10</t>
+          <t>竞技场商店：勇士勋章(19) x150</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:97</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:115</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -2941,7 +2942,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>兑换 高阶记录盘x10；正式 ShopGoods.Price=19,10</t>
+          <t>兑换 定轨组件x1；正式 ShopGoods.Price=19,150</t>
         </is>
       </c>
     </row>
@@ -2963,23 +2964,23 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109005｜ShopId 1109</t>
+          <t>ShopGoods 1109002｜ShopId 1109</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：未知笔记(110) x10</t>
+          <t>竞技场商店：秘制炸鸡桶(105) x1</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x10</t>
+          <t>竞技场商店：勇士勋章(19) x30</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:98</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:107</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -2989,7 +2990,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>兑换 未知笔记x10；正式 ShopGoods.Price=19,10</t>
+          <t>兑换 秘制炸鸡桶x1；正式 ShopGoods.Price=19,30</t>
         </is>
       </c>
     </row>
@@ -3006,28 +3007,28 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109001｜ShopId 1109</t>
+          <t>ShopGoods 1109004｜ShopId 1109</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：熔晶(103) x1</t>
+          <t>竞技场商店：高阶记录盘(102) x10</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x150</t>
+          <t>竞技场商店：勇士勋章(19) x10</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:94</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:109</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -3037,7 +3038,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>兑换 熔晶x1；正式 ShopGoods.Price=19,150</t>
+          <t>兑换 高阶记录盘x10；正式 ShopGoods.Price=19,10</t>
         </is>
       </c>
     </row>
@@ -3054,17 +3055,17 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109003｜ShopId 1109</t>
+          <t>ShopGoods 1109005｜ShopId 1109</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：猎鹰金币(1) x100000</t>
+          <t>竞技场商店：未知笔记(110) x10</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -3075,7 +3076,7 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:96</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:110</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -3085,7 +3086,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>兑换 猎鹰金币x100000；正式 ShopGoods.Price=19,10</t>
+          <t>兑换 未知笔记x10；正式 ShopGoods.Price=19,10</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3108,12 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109006｜ShopId 1109</t>
+          <t>ShopGoods 1109003｜ShopId 1109</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：合淬喷剂(13) x10000</t>
+          <t>竞技场商店：猎鹰金币(1) x100000</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -3123,7 +3124,7 @@
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:99</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:108</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -3133,7 +3134,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>兑换 合淬喷剂x10000；正式 ShopGoods.Price=19,10</t>
+          <t>兑换 猎鹰金币x100000；正式 ShopGoods.Price=19,10</t>
         </is>
       </c>
     </row>
@@ -3150,28 +3151,28 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay50</t>
+          <t>BuyLimit_FourteenDay10</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109007｜ShopId 1109</t>
+          <t>ShopGoods 1109031｜ShopId 1109</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：校准元件(28) x120</t>
+          <t>竞技场商店：收容凭证(107) x1</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店：勇士勋章(19) x10</t>
+          <t>竞技场商店：勇士勋章(19) x15</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:100</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:116</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -3181,7 +3182,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>兑换 校准元件x120；正式 ShopGoods.Price=19,10</t>
+          <t>兑换 收容凭证x1；正式 ShopGoods.Price=19,15</t>
         </is>
       </c>
     </row>
@@ -3193,37 +3194,45 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
+          <t>竞技场商店</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>14天赛季</t>
+          <t>BuyLimit_FourteenDay50</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥5胜</t>
+          <t>ShopGoods 1109007｜ShopId 1109</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：竞技场代币(19) x30</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr"/>
+          <t>竞技场商店：校准元件(28) x120</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>竞技场商店：勇士勋章(19) x10</t>
+        </is>
+      </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:2</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:112</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>直接奖励</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr"/>
+          <t>商店兑换货币；商店兑换商品</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>兑换 校准元件x120；正式 ShopGoods.Price=19,10</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3243,19 +3252,19 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>赛季累胜≥5胜</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：炮台升级小材料(28) x60</t>
+          <t>赛季累胜：竞技场代币(19) x30</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:3</t>
+          <t>配置页-竞技场:2</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -3283,19 +3292,19 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥10胜</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：竞技场代币(19) x60</t>
+          <t>赛季累胜：炮台升级小材料(28) x60</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:4</t>
+          <t>配置页-竞技场:3</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -3323,19 +3332,19 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：炮台升级小材料(28) x60</t>
+          <t>赛季累胜：竞技场代币(19) x60</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:5</t>
+          <t>配置页-竞技场:4</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -3363,19 +3372,19 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥20胜</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：钻石(2) x200</t>
+          <t>赛季累胜：炮台升级小材料(28) x60</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:6</t>
+          <t>配置页-竞技场:5</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -3403,19 +3412,19 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥25胜</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：炮台升级小材料(28) x80</t>
+          <t>赛季累胜：钻石(2) x200</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:7</t>
+          <t>配置页-竞技场:6</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -3443,19 +3452,19 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：竞技场代币(19) x100</t>
+          <t>赛季累胜：炮台升级小材料(28) x80</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:8</t>
+          <t>配置页-竞技场:7</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -3483,19 +3492,19 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥40胜</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：钻石(2) x300</t>
+          <t>赛季累胜：竞技场代币(19) x100</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:9</t>
+          <t>配置页-竞技场:8</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -3523,19 +3532,19 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥60胜</t>
+          <t>赛季累胜≥50胜</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜：炮台升级小材料(28) x400</t>
+          <t>赛季累胜：钻石(2) x300</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:10</t>
+          <t>配置页-竞技场:9</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -3553,7 +3562,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -3563,19 +3572,19 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>达到传说｜积分≥3000</t>
+          <t>赛季累胜≥60胜</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x500</t>
+          <t>赛季累胜：炮台升级小材料(28) x400</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:44</t>
+          <t>配置页-竞技场:10</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -3608,14 +3617,14 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x1200</t>
+          <t>赛季结算奖励：钻石(2) x500</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:45</t>
+          <t>配置页-竞技场:44</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -3643,19 +3652,19 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅰ｜积分≥2900</t>
+          <t>达到传说｜积分≥3000</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x400</t>
+          <t>赛季结算奖励：竞技场代币(19) x1200</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:42</t>
+          <t>配置页-竞技场:45</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -3688,14 +3697,14 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x1150</t>
+          <t>赛季结算奖励：钻石(2) x400</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:43</t>
+          <t>配置页-竞技场:42</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -3723,19 +3732,19 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅱ｜积分≥2800</t>
+          <t>达到大师Ⅰ｜积分≥2900</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x400</t>
+          <t>赛季结算奖励：竞技场代币(19) x1150</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:40</t>
+          <t>配置页-竞技场:43</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -3768,14 +3777,14 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x1100</t>
+          <t>赛季结算奖励：钻石(2) x400</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:41</t>
+          <t>配置页-竞技场:40</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -3803,19 +3812,19 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅲ｜积分≥2700</t>
+          <t>达到大师Ⅱ｜积分≥2800</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x400</t>
+          <t>赛季结算奖励：竞技场代币(19) x1100</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:38</t>
+          <t>配置页-竞技场:41</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -3848,14 +3857,14 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x1050</t>
+          <t>赛季结算奖励：钻石(2) x400</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:39</t>
+          <t>配置页-竞技场:38</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -3883,19 +3892,19 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅰ｜积分≥1400</t>
+          <t>达到大师Ⅲ｜积分≥2700</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x1050</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:12</t>
+          <t>配置页-竞技场:39</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -3928,14 +3937,14 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x400</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:13</t>
+          <t>配置页-竞技场:12</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -3963,19 +3972,19 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅱ｜积分≥1300</t>
+          <t>达到白银Ⅰ｜积分≥1400</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x400</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:10</t>
+          <t>配置页-竞技场:13</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4008,14 +4017,14 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x350</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:11</t>
+          <t>配置页-竞技场:10</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -4043,19 +4052,19 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅲ｜积分≥1200</t>
+          <t>达到白银Ⅱ｜积分≥1300</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x350</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:8</t>
+          <t>配置页-竞技场:11</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -4088,14 +4097,14 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x300</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:9</t>
+          <t>配置页-竞技场:8</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -4123,19 +4132,19 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅰ｜积分≥2300</t>
+          <t>达到白银Ⅲ｜积分≥1200</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x250</t>
+          <t>赛季结算奖励：竞技场代币(19) x300</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:30</t>
+          <t>配置页-竞技场:9</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4168,14 +4177,14 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x850</t>
+          <t>赛季结算奖励：钻石(2) x250</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:31</t>
+          <t>配置页-竞技场:30</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -4203,19 +4212,19 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅱ｜积分≥2200</t>
+          <t>达到翡翠Ⅰ｜积分≥2300</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x250</t>
+          <t>赛季结算奖励：竞技场代币(19) x850</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:28</t>
+          <t>配置页-竞技场:31</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4248,14 +4257,14 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x800</t>
+          <t>赛季结算奖励：钻石(2) x250</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:29</t>
+          <t>配置页-竞技场:28</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -4283,19 +4292,19 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅲ｜积分≥2100</t>
+          <t>达到翡翠Ⅱ｜积分≥2200</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x250</t>
+          <t>赛季结算奖励：竞技场代币(19) x800</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:26</t>
+          <t>配置页-竞技场:29</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4328,14 +4337,14 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x750</t>
+          <t>赛季结算奖励：钻石(2) x250</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:27</t>
+          <t>配置页-竞技场:26</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -4363,19 +4372,19 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅰ｜积分≥2600</t>
+          <t>达到翡翠Ⅲ｜积分≥2100</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x300</t>
+          <t>赛季结算奖励：竞技场代币(19) x750</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:36</t>
+          <t>配置页-竞技场:27</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -4408,14 +4417,14 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x1000</t>
+          <t>赛季结算奖励：钻石(2) x300</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:37</t>
+          <t>配置页-竞技场:36</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -4443,19 +4452,19 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅱ｜积分≥2500</t>
+          <t>达到钻石Ⅰ｜积分≥2600</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x300</t>
+          <t>赛季结算奖励：竞技场代币(19) x1000</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:34</t>
+          <t>配置页-竞技场:37</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -4488,14 +4497,14 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x950</t>
+          <t>赛季结算奖励：钻石(2) x300</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:35</t>
+          <t>配置页-竞技场:34</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -4523,19 +4532,19 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅲ｜积分≥2400</t>
+          <t>达到钻石Ⅱ｜积分≥2500</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x300</t>
+          <t>赛季结算奖励：竞技场代币(19) x950</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:32</t>
+          <t>配置页-竞技场:35</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -4568,14 +4577,14 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x900</t>
+          <t>赛季结算奖励：钻石(2) x300</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr"/>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:33</t>
+          <t>配置页-竞技场:32</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -4603,19 +4612,19 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅰ｜积分≥2000</t>
+          <t>达到钻石Ⅲ｜积分≥2400</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x200</t>
+          <t>赛季结算奖励：竞技场代币(19) x900</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:24</t>
+          <t>配置页-竞技场:33</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -4648,14 +4657,14 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x700</t>
+          <t>赛季结算奖励：钻石(2) x200</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:25</t>
+          <t>配置页-竞技场:24</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
@@ -4683,19 +4692,19 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅱ｜积分≥1900</t>
+          <t>达到铂金Ⅰ｜积分≥2000</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x200</t>
+          <t>赛季结算奖励：竞技场代币(19) x700</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:22</t>
+          <t>配置页-竞技场:25</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -4728,14 +4737,14 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x650</t>
+          <t>赛季结算奖励：钻石(2) x200</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:23</t>
+          <t>配置页-竞技场:22</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
@@ -4763,19 +4772,19 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅲ｜积分≥1800</t>
+          <t>达到铂金Ⅱ｜积分≥1900</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x200</t>
+          <t>赛季结算奖励：竞技场代币(19) x650</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:20</t>
+          <t>配置页-竞技场:23</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
@@ -4808,14 +4817,14 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x600</t>
+          <t>赛季结算奖励：钻石(2) x200</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
       <c r="G95" s="5" t="inlineStr"/>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:21</t>
+          <t>配置页-竞技场:20</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
@@ -4843,19 +4852,19 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅰ｜积分≥1100</t>
+          <t>达到铂金Ⅲ｜积分≥1800</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x600</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:6</t>
+          <t>配置页-竞技场:21</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
@@ -4888,14 +4897,14 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x250</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:7</t>
+          <t>配置页-竞技场:6</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -4923,19 +4932,19 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅱ｜积分≥1000</t>
+          <t>达到青铜Ⅰ｜积分≥1100</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x250</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:4</t>
+          <t>配置页-竞技场:7</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -4968,14 +4977,14 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x200</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
       <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:5</t>
+          <t>配置页-竞技场:4</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -5003,19 +5012,19 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅲ｜积分≥0</t>
+          <t>达到青铜Ⅱ｜积分≥1000</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x100</t>
+          <t>赛季结算奖励：竞技场代币(19) x200</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:2</t>
+          <t>配置页-竞技场:5</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -5048,14 +5057,14 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x100</t>
+          <t>赛季结算奖励：钻石(2) x100</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:3</t>
+          <t>配置页-竞技场:2</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -5083,19 +5092,19 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅰ｜积分≥1700</t>
+          <t>达到青铜Ⅲ｜积分≥0</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x150</t>
+          <t>赛季结算奖励：竞技场代币(19) x100</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:18</t>
+          <t>配置页-竞技场:3</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -5128,14 +5137,14 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x550</t>
+          <t>赛季结算奖励：钻石(2) x150</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:19</t>
+          <t>配置页-竞技场:18</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -5163,19 +5172,19 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅱ｜积分≥1600</t>
+          <t>达到黄金Ⅰ｜积分≥1700</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x150</t>
+          <t>赛季结算奖励：竞技场代币(19) x550</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr"/>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:16</t>
+          <t>配置页-竞技场:19</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -5208,14 +5217,14 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x500</t>
+          <t>赛季结算奖励：钻石(2) x150</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
       <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:17</t>
+          <t>配置页-竞技场:16</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5243,19 +5252,19 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅲ｜积分≥1500</t>
+          <t>达到黄金Ⅱ｜积分≥1600</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：钻石(2) x150</t>
+          <t>赛季结算奖励：竞技场代币(19) x500</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:14</t>
+          <t>配置页-竞技场:17</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -5288,14 +5297,14 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励：竞技场代币(19) x450</t>
+          <t>赛季结算奖励：钻石(2) x150</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:15</t>
+          <t>配置页-竞技场:14</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -5313,29 +5322,29 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励</t>
+          <t>赛季结算奖励</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>生涯一次性</t>
+          <t>14天赛季</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>达到传说｜积分≥3000</t>
+          <t>达到黄金Ⅲ｜积分≥1500</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x1500</t>
+          <t>赛季结算奖励：竞技场代币(19) x450</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:22</t>
+          <t>配置页-竞技场:15</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -5363,19 +5372,19 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅰ｜积分≥2900</t>
+          <t>达到传说｜积分≥3000</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x1000</t>
+          <t>首次到达奖励：钻石(2) x1500</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
       <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:21</t>
+          <t>配置页-竞技场:22</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -5403,19 +5412,19 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅱ｜积分≥2800</t>
+          <t>达到大师Ⅰ｜积分≥2900</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x1000</t>
+          <t>首次到达奖励：竞技场代币(19) x1000</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr"/>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:20</t>
+          <t>配置页-竞技场:21</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -5443,19 +5452,19 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅲ｜积分≥2700</t>
+          <t>达到大师Ⅱ｜积分≥2800</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x1000</t>
+          <t>首次到达奖励：炮台升级小材料(28) x1000</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:19</t>
+          <t>配置页-竞技场:20</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -5483,19 +5492,19 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅰ｜积分≥1400</t>
+          <t>达到大师Ⅲ｜积分≥2700</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x600</t>
+          <t>首次到达奖励：钻石(2) x1000</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:6</t>
+          <t>配置页-竞技场:19</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -5523,19 +5532,19 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅱ｜积分≥1300</t>
+          <t>达到白银Ⅰ｜积分≥1400</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x600</t>
+          <t>首次到达奖励：竞技场代币(19) x600</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:5</t>
+          <t>配置页-竞技场:6</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -5563,19 +5572,19 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅲ｜积分≥1200</t>
+          <t>达到白银Ⅱ｜积分≥1300</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x600</t>
+          <t>首次到达奖励：炮台升级小材料(28) x600</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr"/>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:4</t>
+          <t>配置页-竞技场:5</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -5603,19 +5612,19 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅰ｜积分≥2300</t>
+          <t>达到白银Ⅲ｜积分≥1200</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x800</t>
+          <t>首次到达奖励：钻石(2) x600</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr"/>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:15</t>
+          <t>配置页-竞技场:4</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
@@ -5643,19 +5652,19 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅱ｜积分≥2200</t>
+          <t>达到翡翠Ⅰ｜积分≥2300</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x800</t>
+          <t>首次到达奖励：竞技场代币(19) x800</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:14</t>
+          <t>配置页-竞技场:15</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -5683,19 +5692,19 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅲ｜积分≥2100</t>
+          <t>达到翡翠Ⅱ｜积分≥2200</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x800</t>
+          <t>首次到达奖励：炮台升级小材料(28) x800</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
       <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:13</t>
+          <t>配置页-竞技场:14</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
@@ -5723,19 +5732,19 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅰ｜积分≥2600</t>
+          <t>达到翡翠Ⅲ｜积分≥2100</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x1000</t>
+          <t>首次到达奖励：钻石(2) x800</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:18</t>
+          <t>配置页-竞技场:13</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
@@ -5763,19 +5772,19 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅱ｜积分≥2500</t>
+          <t>达到钻石Ⅰ｜积分≥2600</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x1000</t>
+          <t>首次到达奖励：竞技场代币(19) x1000</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:17</t>
+          <t>配置页-竞技场:18</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -5803,19 +5812,19 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅲ｜积分≥2400</t>
+          <t>达到钻石Ⅱ｜积分≥2500</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x1000</t>
+          <t>首次到达奖励：炮台升级小材料(28) x1000</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:16</t>
+          <t>配置页-竞技场:17</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -5843,19 +5852,19 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅰ｜积分≥2000</t>
+          <t>达到钻石Ⅲ｜积分≥2400</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x800</t>
+          <t>首次到达奖励：钻石(2) x1000</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:12</t>
+          <t>配置页-竞技场:16</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -5883,19 +5892,19 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅱ｜积分≥1900</t>
+          <t>达到铂金Ⅰ｜积分≥2000</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x800</t>
+          <t>首次到达奖励：竞技场代币(19) x800</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:11</t>
+          <t>配置页-竞技场:12</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -5923,19 +5932,19 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅲ｜积分≥1800</t>
+          <t>达到铂金Ⅱ｜积分≥1900</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x800</t>
+          <t>首次到达奖励：炮台升级小材料(28) x800</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
       <c r="G123" s="5" t="inlineStr"/>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:10</t>
+          <t>配置页-竞技场:11</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -5963,19 +5972,19 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅰ｜积分≥1100</t>
+          <t>达到铂金Ⅲ｜积分≥1800</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x400</t>
+          <t>首次到达奖励：钻石(2) x800</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr"/>
       <c r="G124" s="5" t="inlineStr"/>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:3</t>
+          <t>配置页-竞技场:10</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -6003,19 +6012,19 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅱ｜积分≥1000</t>
+          <t>达到青铜Ⅰ｜积分≥1100</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：B炮台(96303) x1</t>
+          <t>首次到达奖励：竞技场代币(19) x400</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:2</t>
+          <t>配置页-竞技场:3</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -6043,19 +6052,19 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅰ｜积分≥1700</t>
+          <t>达到青铜Ⅱ｜积分≥1000</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：竞技场代币(19) x600</t>
+          <t>首次到达奖励：B炮台(96303) x1</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:9</t>
+          <t>配置页-竞技场:2</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -6083,19 +6092,19 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅱ｜积分≥1600</t>
+          <t>达到黄金Ⅰ｜积分≥1700</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：炮台升级小材料(28) x600</t>
+          <t>首次到达奖励：竞技场代币(19) x600</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场:8</t>
+          <t>配置页-竞技场:9</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -6123,30 +6132,70 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅲ｜积分≥1500</t>
+          <t>达到黄金Ⅱ｜积分≥1600</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励：钻石(2) x600</t>
+          <t>首次到达奖励：炮台升级小材料(28) x600</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr">
         <is>
+          <t>配置页-竞技场:8</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>直接奖励</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>竞技场(PVPVE)</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>首次到达奖励</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>生涯一次性</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>达到黄金Ⅲ｜积分≥1500</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>首次到达奖励：钻石(2) x600</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
           <t>配置页-竞技场:7</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>直接奖励</t>
         </is>
       </c>
-      <c r="J128" s="5" t="inlineStr"/>
+      <c r="J129" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
+  <autoFilter ref="A1:J129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6160,7 +6209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V118"/>
+  <dimension ref="A1:W119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6183,8 +6232,9 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="44" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="44" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6218,6 +6268,7 @@
       <c r="T1" s="5" t="n"/>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
+      <c r="W1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n"/>
@@ -6242,6 +6293,7 @@
       <c r="T2" s="5" t="n"/>
       <c r="U2" s="5" t="n"/>
       <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -6291,65 +6343,70 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>产出_元能核心</t>
+          <t>产出_熔晶</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
+          <t>产出_定轨组件</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>产出_秘制炸鸡桶</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
           <t>产出_高阶记录盘</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>产出_未知笔记</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>产出_熔晶</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>产出_猎鹰金币</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>产出_合淬喷剂</t>
-        </is>
-      </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
+          <t>产出_收容凭证</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
           <t>产出_校准元件</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t>产出_钻石</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>产出_B炮台</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>产出价值(钻石)</t>
         </is>
       </c>
-      <c r="T3" s="7" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t>消耗价值(钻石)</t>
         </is>
       </c>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="V3" s="7" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="V3" s="7" t="inlineStr">
+      <c r="W3" s="7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -6392,12 +6449,13 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRankReward.xlsx:5</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6436,12 +6494,13 @@
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRankReward.xlsx:6</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -6480,17 +6539,18 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRankReward.xlsx:7</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥5胜</t>
+          <t>赛季累胜≥3胜</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -6524,12 +6584,13 @@
       <c r="R7" s="5" t="inlineStr"/>
       <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaWinStreak.xlsx:5</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -6566,23 +6627,24 @@
       <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:2</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>赛季累胜≥6胜</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -6616,22 +6678,23 @@
       <c r="R9" s="5" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaWinStreak.xlsx:6</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>赛季累胜≥9胜</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
+          <t>正式赛季累胜引用</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6639,13 +6702,13 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>ArenaWinStreak.DropId x26003003</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
@@ -6658,28 +6721,25 @@
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:3</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:7</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥10胜</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>正式赛季累胜引用</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -6687,13 +6747,13 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>ArenaWinStreak.DropId x26003003</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
@@ -6707,23 +6767,28 @@
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:7</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:3</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥12胜</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
+          <t>正式赛季累胜引用</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -6731,14 +6796,14 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ArenaWinStreak.DropId x26003004</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
@@ -6750,23 +6815,20 @@
       <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr"/>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
+      <c r="S12" s="5" t="inlineStr"/>
       <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:4</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:8</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -6781,7 +6843,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ArenaWinStreak.DropId x26003004</t>
+          <t>ArenaWinStreak.DropId x26003005</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
@@ -6800,17 +6862,18 @@
       <c r="R13" s="5" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:8</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:9</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -6825,12 +6888,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
@@ -6842,23 +6905,24 @@
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:5</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:4</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥18胜</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -6873,7 +6937,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ArenaWinStreak.DropId x26003005</t>
+          <t>ArenaWinStreak.DropId x26003006</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
@@ -6892,17 +6956,18 @@
       <c r="R15" s="5" t="inlineStr"/>
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:9</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:10</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥20胜</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -6917,7 +6982,11 @@
       </c>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
@@ -6928,29 +6997,26 @@
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:6</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:5</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥24胜</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -6965,7 +7031,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ArenaWinStreak.DropId x26003006</t>
+          <t>ArenaWinStreak.DropId x26003007</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
@@ -6984,17 +7050,18 @@
       <c r="R17" s="5" t="inlineStr"/>
       <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:10</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:11</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥25胜</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -7009,11 +7076,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
@@ -7025,24 +7088,29 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr"/>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:7</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:6</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥27胜</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -7057,7 +7125,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>ArenaWinStreak.DropId x26003007</t>
+          <t>ArenaWinStreak.DropId x26003008</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
@@ -7076,22 +7144,23 @@
       <c r="R19" s="5" t="inlineStr"/>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:11</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:12</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
+          <t>正式赛季累胜引用</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -7099,14 +7168,14 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>ArenaWinStreak.DropId x26003009</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
@@ -7118,28 +7187,25 @@
       <c r="P20" s="5" t="inlineStr"/>
       <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="S20" s="5" t="inlineStr"/>
       <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:8</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinStreak.xlsx:13</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>正式赛季累胜引用</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -7147,13 +7213,13 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>ArenaWinStreak.DropId x26003008</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -7167,18 +7233,23 @@
       <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr"/>
       <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:12</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:7</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥40胜</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -7194,7 +7265,11 @@
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
@@ -7204,34 +7279,31 @@
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>配置页-竞技场:9</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:8</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥60胜</t>
+          <t>赛季累胜≥50胜</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>正式赛季累胜引用</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -7239,11 +7311,7 @@
           <t>14天赛季</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>ArenaWinStreak.DropId x26003009</t>
-        </is>
-      </c>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
@@ -7257,15 +7325,24 @@
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
       <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinStreak.xlsx:13</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场:9</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -7302,18 +7379,19 @@
       <c r="P24" s="5" t="inlineStr"/>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr">
+      <c r="S24" s="5" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:10</t>
         </is>
       </c>
-      <c r="V24" s="5" t="inlineStr"/>
+      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -7344,24 +7422,25 @@
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
+      <c r="S25" s="5" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:22</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr"/>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -7392,24 +7471,25 @@
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr">
+      <c r="S26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr">
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:44</t>
         </is>
       </c>
-      <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -7446,18 +7526,19 @@
       <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:45</t>
         </is>
       </c>
-      <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7496,12 +7577,13 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr">
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:16</t>
         </is>
       </c>
-      <c r="V28" s="5" t="inlineStr"/>
+      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -7538,18 +7620,19 @@
       <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
+      <c r="S29" s="5" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:21</t>
         </is>
       </c>
-      <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -7580,24 +7663,25 @@
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr">
+      <c r="S30" s="5" t="inlineStr"/>
+      <c r="T30" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr">
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:42</t>
         </is>
       </c>
-      <c r="V30" s="5" t="inlineStr"/>
+      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -7634,18 +7718,19 @@
       <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>11500</t>
         </is>
       </c>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:43</t>
         </is>
       </c>
-      <c r="V31" s="5" t="inlineStr"/>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -7684,12 +7769,13 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr">
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:15</t>
         </is>
       </c>
-      <c r="V32" s="5" t="inlineStr"/>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -7726,18 +7812,19 @@
       <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr">
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:20</t>
         </is>
       </c>
-      <c r="V33" s="5" t="inlineStr"/>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -7768,24 +7855,25 @@
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr"/>
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr">
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:40</t>
         </is>
       </c>
-      <c r="V34" s="5" t="inlineStr"/>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -7822,18 +7910,19 @@
       <c r="P35" s="5" t="inlineStr"/>
       <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr">
+      <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:41</t>
         </is>
       </c>
-      <c r="V35" s="5" t="inlineStr"/>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -7872,12 +7961,13 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr">
+      <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:14</t>
         </is>
       </c>
-      <c r="V36" s="5" t="inlineStr"/>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -7908,24 +7998,25 @@
       <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr">
+      <c r="S37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
+      <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:19</t>
         </is>
       </c>
-      <c r="V37" s="5" t="inlineStr"/>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -7956,24 +8047,25 @@
       <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
+      <c r="S38" s="5" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
+      <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:38</t>
         </is>
       </c>
-      <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -8010,18 +8102,19 @@
       <c r="P39" s="5" t="inlineStr"/>
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr">
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>10500</t>
         </is>
       </c>
-      <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr">
+      <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:39</t>
         </is>
       </c>
-      <c r="V39" s="5" t="inlineStr"/>
+      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -8058,18 +8151,19 @@
       <c r="P40" s="5" t="inlineStr"/>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr">
+      <c r="S40" s="5" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr">
+      <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:6</t>
         </is>
       </c>
-      <c r="V40" s="5" t="inlineStr"/>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -8100,24 +8194,25 @@
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr">
+      <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:12</t>
         </is>
       </c>
-      <c r="V41" s="5" t="inlineStr"/>
+      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -8154,18 +8249,19 @@
       <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:13</t>
         </is>
       </c>
-      <c r="V42" s="5" t="inlineStr"/>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -8202,18 +8298,19 @@
       <c r="P43" s="5" t="inlineStr"/>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:5</t>
         </is>
       </c>
-      <c r="V43" s="5" t="inlineStr"/>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -8244,24 +8341,25 @@
       <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr">
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr">
+      <c r="S44" s="5" t="inlineStr"/>
+      <c r="T44" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr">
+      <c r="U44" s="5" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:10</t>
         </is>
       </c>
-      <c r="V44" s="5" t="inlineStr"/>
+      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -8298,18 +8396,19 @@
       <c r="P45" s="5" t="inlineStr"/>
       <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
+      <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:11</t>
         </is>
       </c>
-      <c r="V45" s="5" t="inlineStr"/>
+      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -8340,24 +8439,25 @@
       <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:4</t>
         </is>
       </c>
-      <c r="V46" s="5" t="inlineStr"/>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -8388,24 +8488,25 @@
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
+      <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:8</t>
         </is>
       </c>
-      <c r="V47" s="5" t="inlineStr"/>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -8442,18 +8543,19 @@
       <c r="P48" s="5" t="inlineStr"/>
       <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr">
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr">
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:9</t>
         </is>
       </c>
-      <c r="V48" s="5" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -8490,18 +8592,19 @@
       <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
+      <c r="S49" s="5" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr">
+      <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:15</t>
         </is>
       </c>
-      <c r="V49" s="5" t="inlineStr"/>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -8532,24 +8635,25 @@
       <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr">
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
+      <c r="S50" s="5" t="inlineStr"/>
+      <c r="T50" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr">
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:30</t>
         </is>
       </c>
-      <c r="V50" s="5" t="inlineStr"/>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -8586,18 +8690,19 @@
       <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
+      <c r="S51" s="5" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>8500</t>
         </is>
       </c>
-      <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr">
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:31</t>
         </is>
       </c>
-      <c r="V51" s="5" t="inlineStr"/>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -8634,18 +8739,19 @@
       <c r="P52" s="5" t="inlineStr"/>
       <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr">
+      <c r="S52" s="5" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr">
+      <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:14</t>
         </is>
       </c>
-      <c r="V52" s="5" t="inlineStr"/>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -8676,24 +8782,25 @@
       <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr">
+      <c r="S53" s="5" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr">
+      <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:28</t>
         </is>
       </c>
-      <c r="V53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -8730,18 +8837,19 @@
       <c r="P54" s="5" t="inlineStr"/>
       <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr">
+      <c r="S54" s="5" t="inlineStr"/>
+      <c r="T54" s="5" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr">
+      <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:29</t>
         </is>
       </c>
-      <c r="V54" s="5" t="inlineStr"/>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -8772,24 +8880,25 @@
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr">
+      <c r="S55" s="5" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr">
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:13</t>
         </is>
       </c>
-      <c r="V55" s="5" t="inlineStr"/>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -8820,24 +8929,25 @@
       <c r="N56" s="5" t="inlineStr"/>
       <c r="O56" s="5" t="inlineStr"/>
       <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr">
+      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="R56" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr">
+      <c r="S56" s="5" t="inlineStr"/>
+      <c r="T56" s="5" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="T56" s="5" t="inlineStr"/>
-      <c r="U56" s="5" t="inlineStr">
+      <c r="U56" s="5" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:26</t>
         </is>
       </c>
-      <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -8874,18 +8984,19 @@
       <c r="P57" s="5" t="inlineStr"/>
       <c r="Q57" s="5" t="inlineStr"/>
       <c r="R57" s="5" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr">
+      <c r="S57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr">
         <is>
           <t>7500</t>
         </is>
       </c>
-      <c r="T57" s="5" t="inlineStr"/>
-      <c r="U57" s="5" t="inlineStr">
+      <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:27</t>
         </is>
       </c>
-      <c r="V57" s="5" t="inlineStr"/>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -8924,12 +9035,13 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="5" t="inlineStr"/>
       <c r="T58" s="5" t="inlineStr"/>
-      <c r="U58" s="5" t="inlineStr">
+      <c r="U58" s="5" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:13</t>
         </is>
       </c>
-      <c r="V58" s="5" t="inlineStr"/>
+      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -8966,18 +9078,19 @@
       <c r="P59" s="5" t="inlineStr"/>
       <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr">
+      <c r="S59" s="5" t="inlineStr"/>
+      <c r="T59" s="5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="T59" s="5" t="inlineStr"/>
-      <c r="U59" s="5" t="inlineStr">
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:18</t>
         </is>
       </c>
-      <c r="V59" s="5" t="inlineStr"/>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -9008,24 +9121,25 @@
       <c r="N60" s="5" t="inlineStr"/>
       <c r="O60" s="5" t="inlineStr"/>
       <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="R60" s="5" t="inlineStr"/>
-      <c r="S60" s="5" t="inlineStr">
+      <c r="S60" s="5" t="inlineStr"/>
+      <c r="T60" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="T60" s="5" t="inlineStr"/>
-      <c r="U60" s="5" t="inlineStr">
+      <c r="U60" s="5" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:36</t>
         </is>
       </c>
-      <c r="V60" s="5" t="inlineStr"/>
+      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -9062,18 +9176,19 @@
       <c r="P61" s="5" t="inlineStr"/>
       <c r="Q61" s="5" t="inlineStr"/>
       <c r="R61" s="5" t="inlineStr"/>
-      <c r="S61" s="5" t="inlineStr">
+      <c r="S61" s="5" t="inlineStr"/>
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="T61" s="5" t="inlineStr"/>
-      <c r="U61" s="5" t="inlineStr">
+      <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:37</t>
         </is>
       </c>
-      <c r="V61" s="5" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -9112,12 +9227,13 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="5" t="inlineStr"/>
       <c r="T62" s="5" t="inlineStr"/>
-      <c r="U62" s="5" t="inlineStr">
+      <c r="U62" s="5" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:12</t>
         </is>
       </c>
-      <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -9154,18 +9270,19 @@
       <c r="P63" s="5" t="inlineStr"/>
       <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="inlineStr"/>
-      <c r="S63" s="5" t="inlineStr">
+      <c r="S63" s="5" t="inlineStr"/>
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T63" s="5" t="inlineStr"/>
-      <c r="U63" s="5" t="inlineStr">
+      <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:17</t>
         </is>
       </c>
-      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -9196,24 +9313,25 @@
       <c r="N64" s="5" t="inlineStr"/>
       <c r="O64" s="5" t="inlineStr"/>
       <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr">
+      <c r="Q64" s="5" t="inlineStr"/>
+      <c r="R64" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="S64" s="5" t="inlineStr"/>
+      <c r="T64" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="T64" s="5" t="inlineStr"/>
-      <c r="U64" s="5" t="inlineStr">
+      <c r="U64" s="5" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:34</t>
         </is>
       </c>
-      <c r="V64" s="5" t="inlineStr"/>
+      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -9250,18 +9368,19 @@
       <c r="P65" s="5" t="inlineStr"/>
       <c r="Q65" s="5" t="inlineStr"/>
       <c r="R65" s="5" t="inlineStr"/>
-      <c r="S65" s="5" t="inlineStr">
+      <c r="S65" s="5" t="inlineStr"/>
+      <c r="T65" s="5" t="inlineStr">
         <is>
           <t>9500</t>
         </is>
       </c>
-      <c r="T65" s="5" t="inlineStr"/>
-      <c r="U65" s="5" t="inlineStr">
+      <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:35</t>
         </is>
       </c>
-      <c r="V65" s="5" t="inlineStr"/>
+      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -9300,12 +9419,13 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="5" t="inlineStr"/>
       <c r="T66" s="5" t="inlineStr"/>
-      <c r="U66" s="5" t="inlineStr">
+      <c r="U66" s="5" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:11</t>
         </is>
       </c>
-      <c r="V66" s="5" t="inlineStr"/>
+      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -9336,24 +9456,25 @@
       <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="5" t="inlineStr"/>
       <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="5" t="inlineStr">
+      <c r="S67" s="5" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T67" s="5" t="inlineStr"/>
-      <c r="U67" s="5" t="inlineStr">
+      <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:16</t>
         </is>
       </c>
-      <c r="V67" s="5" t="inlineStr"/>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -9384,24 +9505,25 @@
       <c r="N68" s="5" t="inlineStr"/>
       <c r="O68" s="5" t="inlineStr"/>
       <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="5" t="inlineStr">
+      <c r="Q68" s="5" t="inlineStr"/>
+      <c r="R68" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="R68" s="5" t="inlineStr"/>
-      <c r="S68" s="5" t="inlineStr">
+      <c r="S68" s="5" t="inlineStr"/>
+      <c r="T68" s="5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="T68" s="5" t="inlineStr"/>
-      <c r="U68" s="5" t="inlineStr">
+      <c r="U68" s="5" t="inlineStr"/>
+      <c r="V68" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:32</t>
         </is>
       </c>
-      <c r="V68" s="5" t="inlineStr"/>
+      <c r="W68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -9438,18 +9560,19 @@
       <c r="P69" s="5" t="inlineStr"/>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="inlineStr"/>
-      <c r="S69" s="5" t="inlineStr">
+      <c r="S69" s="5" t="inlineStr"/>
+      <c r="T69" s="5" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="T69" s="5" t="inlineStr"/>
-      <c r="U69" s="5" t="inlineStr">
+      <c r="U69" s="5" t="inlineStr"/>
+      <c r="V69" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:33</t>
         </is>
       </c>
-      <c r="V69" s="5" t="inlineStr"/>
+      <c r="W69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -9488,12 +9611,13 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="5" t="inlineStr"/>
       <c r="T70" s="5" t="inlineStr"/>
-      <c r="U70" s="5" t="inlineStr">
+      <c r="U70" s="5" t="inlineStr"/>
+      <c r="V70" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:10</t>
         </is>
       </c>
-      <c r="V70" s="5" t="inlineStr"/>
+      <c r="W70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -9530,18 +9654,19 @@
       <c r="P71" s="5" t="inlineStr"/>
       <c r="Q71" s="5" t="inlineStr"/>
       <c r="R71" s="5" t="inlineStr"/>
-      <c r="S71" s="5" t="inlineStr">
+      <c r="S71" s="5" t="inlineStr"/>
+      <c r="T71" s="5" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="T71" s="5" t="inlineStr"/>
-      <c r="U71" s="5" t="inlineStr">
+      <c r="U71" s="5" t="inlineStr"/>
+      <c r="V71" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:12</t>
         </is>
       </c>
-      <c r="V71" s="5" t="inlineStr"/>
+      <c r="W71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -9572,24 +9697,25 @@
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
       <c r="P72" s="5" t="inlineStr"/>
-      <c r="Q72" s="5" t="inlineStr">
+      <c r="Q72" s="5" t="inlineStr"/>
+      <c r="R72" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R72" s="5" t="inlineStr"/>
-      <c r="S72" s="5" t="inlineStr">
+      <c r="S72" s="5" t="inlineStr"/>
+      <c r="T72" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="T72" s="5" t="inlineStr"/>
-      <c r="U72" s="5" t="inlineStr">
+      <c r="U72" s="5" t="inlineStr"/>
+      <c r="V72" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:24</t>
         </is>
       </c>
-      <c r="V72" s="5" t="inlineStr"/>
+      <c r="W72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -9626,18 +9752,19 @@
       <c r="P73" s="5" t="inlineStr"/>
       <c r="Q73" s="5" t="inlineStr"/>
       <c r="R73" s="5" t="inlineStr"/>
-      <c r="S73" s="5" t="inlineStr">
+      <c r="S73" s="5" t="inlineStr"/>
+      <c r="T73" s="5" t="inlineStr">
         <is>
           <t>7000</t>
         </is>
       </c>
-      <c r="T73" s="5" t="inlineStr"/>
-      <c r="U73" s="5" t="inlineStr">
+      <c r="U73" s="5" t="inlineStr"/>
+      <c r="V73" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:25</t>
         </is>
       </c>
-      <c r="V73" s="5" t="inlineStr"/>
+      <c r="W73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -9676,12 +9803,13 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="5" t="inlineStr"/>
       <c r="T74" s="5" t="inlineStr"/>
-      <c r="U74" s="5" t="inlineStr">
+      <c r="U74" s="5" t="inlineStr"/>
+      <c r="V74" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:9</t>
         </is>
       </c>
-      <c r="V74" s="5" t="inlineStr"/>
+      <c r="W74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -9718,18 +9846,19 @@
       <c r="P75" s="5" t="inlineStr"/>
       <c r="Q75" s="5" t="inlineStr"/>
       <c r="R75" s="5" t="inlineStr"/>
-      <c r="S75" s="5" t="inlineStr">
+      <c r="S75" s="5" t="inlineStr"/>
+      <c r="T75" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="T75" s="5" t="inlineStr"/>
-      <c r="U75" s="5" t="inlineStr">
+      <c r="U75" s="5" t="inlineStr"/>
+      <c r="V75" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:11</t>
         </is>
       </c>
-      <c r="V75" s="5" t="inlineStr"/>
+      <c r="W75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -9760,24 +9889,25 @@
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr"/>
       <c r="P76" s="5" t="inlineStr"/>
-      <c r="Q76" s="5" t="inlineStr">
+      <c r="Q76" s="5" t="inlineStr"/>
+      <c r="R76" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R76" s="5" t="inlineStr"/>
-      <c r="S76" s="5" t="inlineStr">
+      <c r="S76" s="5" t="inlineStr"/>
+      <c r="T76" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="T76" s="5" t="inlineStr"/>
-      <c r="U76" s="5" t="inlineStr">
+      <c r="U76" s="5" t="inlineStr"/>
+      <c r="V76" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:22</t>
         </is>
       </c>
-      <c r="V76" s="5" t="inlineStr"/>
+      <c r="W76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -9814,18 +9944,19 @@
       <c r="P77" s="5" t="inlineStr"/>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="inlineStr"/>
-      <c r="S77" s="5" t="inlineStr">
+      <c r="S77" s="5" t="inlineStr"/>
+      <c r="T77" s="5" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="T77" s="5" t="inlineStr"/>
-      <c r="U77" s="5" t="inlineStr">
+      <c r="U77" s="5" t="inlineStr"/>
+      <c r="V77" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:23</t>
         </is>
       </c>
-      <c r="V77" s="5" t="inlineStr"/>
+      <c r="W77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -9864,12 +9995,13 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="5" t="inlineStr"/>
       <c r="T78" s="5" t="inlineStr"/>
-      <c r="U78" s="5" t="inlineStr">
+      <c r="U78" s="5" t="inlineStr"/>
+      <c r="V78" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:8</t>
         </is>
       </c>
-      <c r="V78" s="5" t="inlineStr"/>
+      <c r="W78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -9900,24 +10032,25 @@
       <c r="N79" s="5" t="inlineStr"/>
       <c r="O79" s="5" t="inlineStr"/>
       <c r="P79" s="5" t="inlineStr"/>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr"/>
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="R79" s="5" t="inlineStr"/>
-      <c r="S79" s="5" t="inlineStr">
+      <c r="S79" s="5" t="inlineStr"/>
+      <c r="T79" s="5" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="T79" s="5" t="inlineStr"/>
-      <c r="U79" s="5" t="inlineStr">
+      <c r="U79" s="5" t="inlineStr"/>
+      <c r="V79" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:10</t>
         </is>
       </c>
-      <c r="V79" s="5" t="inlineStr"/>
+      <c r="W79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -9948,24 +10081,25 @@
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="inlineStr"/>
-      <c r="Q80" s="5" t="inlineStr">
+      <c r="Q80" s="5" t="inlineStr"/>
+      <c r="R80" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R80" s="5" t="inlineStr"/>
-      <c r="S80" s="5" t="inlineStr">
+      <c r="S80" s="5" t="inlineStr"/>
+      <c r="T80" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="T80" s="5" t="inlineStr"/>
-      <c r="U80" s="5" t="inlineStr">
+      <c r="U80" s="5" t="inlineStr"/>
+      <c r="V80" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:20</t>
         </is>
       </c>
-      <c r="V80" s="5" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -10002,18 +10136,19 @@
       <c r="P81" s="5" t="inlineStr"/>
       <c r="Q81" s="5" t="inlineStr"/>
       <c r="R81" s="5" t="inlineStr"/>
-      <c r="S81" s="5" t="inlineStr">
+      <c r="S81" s="5" t="inlineStr"/>
+      <c r="T81" s="5" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="T81" s="5" t="inlineStr"/>
-      <c r="U81" s="5" t="inlineStr">
+      <c r="U81" s="5" t="inlineStr"/>
+      <c r="V81" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:21</t>
         </is>
       </c>
-      <c r="V81" s="5" t="inlineStr"/>
+      <c r="W81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -10050,18 +10185,19 @@
       <c r="P82" s="5" t="inlineStr"/>
       <c r="Q82" s="5" t="inlineStr"/>
       <c r="R82" s="5" t="inlineStr"/>
-      <c r="S82" s="5" t="inlineStr">
+      <c r="S82" s="5" t="inlineStr"/>
+      <c r="T82" s="5" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="T82" s="5" t="inlineStr"/>
-      <c r="U82" s="5" t="inlineStr">
+      <c r="U82" s="5" t="inlineStr"/>
+      <c r="V82" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:3</t>
         </is>
       </c>
-      <c r="V82" s="5" t="inlineStr"/>
+      <c r="W82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -10092,24 +10228,25 @@
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="5" t="inlineStr"/>
       <c r="P83" s="5" t="inlineStr"/>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R83" s="5" t="inlineStr"/>
-      <c r="S83" s="5" t="inlineStr">
+      <c r="S83" s="5" t="inlineStr"/>
+      <c r="T83" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T83" s="5" t="inlineStr"/>
-      <c r="U83" s="5" t="inlineStr">
+      <c r="U83" s="5" t="inlineStr"/>
+      <c r="V83" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:6</t>
         </is>
       </c>
-      <c r="V83" s="5" t="inlineStr"/>
+      <c r="W83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -10146,18 +10283,19 @@
       <c r="P84" s="5" t="inlineStr"/>
       <c r="Q84" s="5" t="inlineStr"/>
       <c r="R84" s="5" t="inlineStr"/>
-      <c r="S84" s="5" t="inlineStr">
+      <c r="S84" s="5" t="inlineStr"/>
+      <c r="T84" s="5" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="T84" s="5" t="inlineStr"/>
-      <c r="U84" s="5" t="inlineStr">
+      <c r="U84" s="5" t="inlineStr"/>
+      <c r="V84" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:7</t>
         </is>
       </c>
-      <c r="V84" s="5" t="inlineStr"/>
+      <c r="W84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -10189,23 +10327,24 @@
       <c r="O85" s="5" t="inlineStr"/>
       <c r="P85" s="5" t="inlineStr"/>
       <c r="Q85" s="5" t="inlineStr"/>
-      <c r="R85" s="5" t="inlineStr">
+      <c r="R85" s="5" t="inlineStr"/>
+      <c r="S85" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S85" s="5" t="inlineStr">
+      <c r="T85" s="5" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="T85" s="5" t="inlineStr"/>
-      <c r="U85" s="5" t="inlineStr">
+      <c r="U85" s="5" t="inlineStr"/>
+      <c r="V85" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:2</t>
         </is>
       </c>
-      <c r="V85" s="5" t="inlineStr"/>
+      <c r="W85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -10236,24 +10375,25 @@
       <c r="N86" s="5" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
       <c r="P86" s="5" t="inlineStr"/>
-      <c r="Q86" s="5" t="inlineStr">
+      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="R86" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R86" s="5" t="inlineStr"/>
-      <c r="S86" s="5" t="inlineStr">
+      <c r="S86" s="5" t="inlineStr"/>
+      <c r="T86" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T86" s="5" t="inlineStr"/>
-      <c r="U86" s="5" t="inlineStr">
+      <c r="U86" s="5" t="inlineStr"/>
+      <c r="V86" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:4</t>
         </is>
       </c>
-      <c r="V86" s="5" t="inlineStr"/>
+      <c r="W86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -10290,18 +10430,19 @@
       <c r="P87" s="5" t="inlineStr"/>
       <c r="Q87" s="5" t="inlineStr"/>
       <c r="R87" s="5" t="inlineStr"/>
-      <c r="S87" s="5" t="inlineStr">
+      <c r="S87" s="5" t="inlineStr"/>
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="T87" s="5" t="inlineStr"/>
-      <c r="U87" s="5" t="inlineStr">
+      <c r="U87" s="5" t="inlineStr"/>
+      <c r="V87" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:5</t>
         </is>
       </c>
-      <c r="V87" s="5" t="inlineStr"/>
+      <c r="W87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -10332,24 +10473,25 @@
       <c r="N88" s="5" t="inlineStr"/>
       <c r="O88" s="5" t="inlineStr"/>
       <c r="P88" s="5" t="inlineStr"/>
-      <c r="Q88" s="5" t="inlineStr">
+      <c r="Q88" s="5" t="inlineStr"/>
+      <c r="R88" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R88" s="5" t="inlineStr"/>
-      <c r="S88" s="5" t="inlineStr">
+      <c r="S88" s="5" t="inlineStr"/>
+      <c r="T88" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T88" s="5" t="inlineStr"/>
-      <c r="U88" s="5" t="inlineStr">
+      <c r="U88" s="5" t="inlineStr"/>
+      <c r="V88" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:2</t>
         </is>
       </c>
-      <c r="V88" s="5" t="inlineStr"/>
+      <c r="W88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -10386,18 +10528,19 @@
       <c r="P89" s="5" t="inlineStr"/>
       <c r="Q89" s="5" t="inlineStr"/>
       <c r="R89" s="5" t="inlineStr"/>
-      <c r="S89" s="5" t="inlineStr">
+      <c r="S89" s="5" t="inlineStr"/>
+      <c r="T89" s="5" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T89" s="5" t="inlineStr"/>
-      <c r="U89" s="5" t="inlineStr">
+      <c r="U89" s="5" t="inlineStr"/>
+      <c r="V89" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:3</t>
         </is>
       </c>
-      <c r="V89" s="5" t="inlineStr"/>
+      <c r="W89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -10436,12 +10579,13 @@
       <c r="R90" s="5" t="inlineStr"/>
       <c r="S90" s="5" t="inlineStr"/>
       <c r="T90" s="5" t="inlineStr"/>
-      <c r="U90" s="5" t="inlineStr">
+      <c r="U90" s="5" t="inlineStr"/>
+      <c r="V90" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:7</t>
         </is>
       </c>
-      <c r="V90" s="5" t="inlineStr"/>
+      <c r="W90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -10478,18 +10622,19 @@
       <c r="P91" s="5" t="inlineStr"/>
       <c r="Q91" s="5" t="inlineStr"/>
       <c r="R91" s="5" t="inlineStr"/>
-      <c r="S91" s="5" t="inlineStr">
+      <c r="S91" s="5" t="inlineStr"/>
+      <c r="T91" s="5" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="T91" s="5" t="inlineStr"/>
-      <c r="U91" s="5" t="inlineStr">
+      <c r="U91" s="5" t="inlineStr"/>
+      <c r="V91" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:9</t>
         </is>
       </c>
-      <c r="V91" s="5" t="inlineStr"/>
+      <c r="W91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -10520,24 +10665,25 @@
       <c r="N92" s="5" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
       <c r="P92" s="5" t="inlineStr"/>
-      <c r="Q92" s="5" t="inlineStr">
+      <c r="Q92" s="5" t="inlineStr"/>
+      <c r="R92" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="R92" s="5" t="inlineStr"/>
-      <c r="S92" s="5" t="inlineStr">
+      <c r="S92" s="5" t="inlineStr"/>
+      <c r="T92" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T92" s="5" t="inlineStr"/>
-      <c r="U92" s="5" t="inlineStr">
+      <c r="U92" s="5" t="inlineStr"/>
+      <c r="V92" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:18</t>
         </is>
       </c>
-      <c r="V92" s="5" t="inlineStr"/>
+      <c r="W92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -10574,18 +10720,19 @@
       <c r="P93" s="5" t="inlineStr"/>
       <c r="Q93" s="5" t="inlineStr"/>
       <c r="R93" s="5" t="inlineStr"/>
-      <c r="S93" s="5" t="inlineStr">
+      <c r="S93" s="5" t="inlineStr"/>
+      <c r="T93" s="5" t="inlineStr">
         <is>
           <t>5500</t>
         </is>
       </c>
-      <c r="T93" s="5" t="inlineStr"/>
-      <c r="U93" s="5" t="inlineStr">
+      <c r="U93" s="5" t="inlineStr"/>
+      <c r="V93" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:19</t>
         </is>
       </c>
-      <c r="V93" s="5" t="inlineStr"/>
+      <c r="W93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -10624,12 +10771,13 @@
       <c r="R94" s="5" t="inlineStr"/>
       <c r="S94" s="5" t="inlineStr"/>
       <c r="T94" s="5" t="inlineStr"/>
-      <c r="U94" s="5" t="inlineStr">
+      <c r="U94" s="5" t="inlineStr"/>
+      <c r="V94" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:6</t>
         </is>
       </c>
-      <c r="V94" s="5" t="inlineStr"/>
+      <c r="W94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -10666,18 +10814,19 @@
       <c r="P95" s="5" t="inlineStr"/>
       <c r="Q95" s="5" t="inlineStr"/>
       <c r="R95" s="5" t="inlineStr"/>
-      <c r="S95" s="5" t="inlineStr">
+      <c r="S95" s="5" t="inlineStr"/>
+      <c r="T95" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="T95" s="5" t="inlineStr"/>
-      <c r="U95" s="5" t="inlineStr">
+      <c r="U95" s="5" t="inlineStr"/>
+      <c r="V95" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:8</t>
         </is>
       </c>
-      <c r="V95" s="5" t="inlineStr"/>
+      <c r="W95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -10708,24 +10857,25 @@
       <c r="N96" s="5" t="inlineStr"/>
       <c r="O96" s="5" t="inlineStr"/>
       <c r="P96" s="5" t="inlineStr"/>
-      <c r="Q96" s="5" t="inlineStr">
+      <c r="Q96" s="5" t="inlineStr"/>
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="R96" s="5" t="inlineStr"/>
-      <c r="S96" s="5" t="inlineStr">
+      <c r="S96" s="5" t="inlineStr"/>
+      <c r="T96" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T96" s="5" t="inlineStr"/>
-      <c r="U96" s="5" t="inlineStr">
+      <c r="U96" s="5" t="inlineStr"/>
+      <c r="V96" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:16</t>
         </is>
       </c>
-      <c r="V96" s="5" t="inlineStr"/>
+      <c r="W96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -10762,18 +10912,19 @@
       <c r="P97" s="5" t="inlineStr"/>
       <c r="Q97" s="5" t="inlineStr"/>
       <c r="R97" s="5" t="inlineStr"/>
-      <c r="S97" s="5" t="inlineStr">
+      <c r="S97" s="5" t="inlineStr"/>
+      <c r="T97" s="5" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="T97" s="5" t="inlineStr"/>
-      <c r="U97" s="5" t="inlineStr">
+      <c r="U97" s="5" t="inlineStr"/>
+      <c r="V97" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:17</t>
         </is>
       </c>
-      <c r="V97" s="5" t="inlineStr"/>
+      <c r="W97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -10812,12 +10963,13 @@
       <c r="R98" s="5" t="inlineStr"/>
       <c r="S98" s="5" t="inlineStr"/>
       <c r="T98" s="5" t="inlineStr"/>
-      <c r="U98" s="5" t="inlineStr">
+      <c r="U98" s="5" t="inlineStr"/>
+      <c r="V98" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaRank.xlsx:5</t>
         </is>
       </c>
-      <c r="V98" s="5" t="inlineStr"/>
+      <c r="W98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -10848,24 +11000,25 @@
       <c r="N99" s="5" t="inlineStr"/>
       <c r="O99" s="5" t="inlineStr"/>
       <c r="P99" s="5" t="inlineStr"/>
-      <c r="Q99" s="5" t="inlineStr">
+      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="R99" s="5" t="inlineStr"/>
-      <c r="S99" s="5" t="inlineStr">
+      <c r="S99" s="5" t="inlineStr"/>
+      <c r="T99" s="5" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="T99" s="5" t="inlineStr"/>
-      <c r="U99" s="5" t="inlineStr">
+      <c r="U99" s="5" t="inlineStr"/>
+      <c r="V99" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:7</t>
         </is>
       </c>
-      <c r="V99" s="5" t="inlineStr"/>
+      <c r="W99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -10896,24 +11049,25 @@
       <c r="N100" s="5" t="inlineStr"/>
       <c r="O100" s="5" t="inlineStr"/>
       <c r="P100" s="5" t="inlineStr"/>
-      <c r="Q100" s="5" t="inlineStr">
+      <c r="Q100" s="5" t="inlineStr"/>
+      <c r="R100" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="R100" s="5" t="inlineStr"/>
-      <c r="S100" s="5" t="inlineStr">
+      <c r="S100" s="5" t="inlineStr"/>
+      <c r="T100" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T100" s="5" t="inlineStr"/>
-      <c r="U100" s="5" t="inlineStr">
+      <c r="U100" s="5" t="inlineStr"/>
+      <c r="V100" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:14</t>
         </is>
       </c>
-      <c r="V100" s="5" t="inlineStr"/>
+      <c r="W100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -10950,18 +11104,19 @@
       <c r="P101" s="5" t="inlineStr"/>
       <c r="Q101" s="5" t="inlineStr"/>
       <c r="R101" s="5" t="inlineStr"/>
-      <c r="S101" s="5" t="inlineStr">
+      <c r="S101" s="5" t="inlineStr"/>
+      <c r="T101" s="5" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="T101" s="5" t="inlineStr"/>
-      <c r="U101" s="5" t="inlineStr">
+      <c r="U101" s="5" t="inlineStr"/>
+      <c r="V101" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场:15</t>
         </is>
       </c>
-      <c r="V101" s="5" t="inlineStr"/>
+      <c r="W101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -10976,7 +11131,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
@@ -10989,14 +11144,14 @@
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr"/>
-      <c r="J102" s="5" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="M102" s="5" t="inlineStr"/>
       <c r="N102" s="5" t="inlineStr"/>
       <c r="O102" s="5" t="inlineStr"/>
       <c r="P102" s="5" t="inlineStr"/>
@@ -11004,12 +11159,13 @@
       <c r="R102" s="5" t="inlineStr"/>
       <c r="S102" s="5" t="inlineStr"/>
       <c r="T102" s="5" t="inlineStr"/>
-      <c r="U102" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:94</t>
-        </is>
-      </c>
+      <c r="U102" s="5" t="inlineStr"/>
       <c r="V102" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:106</t>
+        </is>
+      </c>
+      <c r="W102" s="5" t="inlineStr">
         <is>
           <t>正式 ShopGoods.Price=19,150；兑换 熔晶x1</t>
         </is>
@@ -11041,13 +11197,13 @@
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
-      <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
       <c r="N103" s="5" t="inlineStr"/>
       <c r="O103" s="5" t="inlineStr"/>
@@ -11056,14 +11212,15 @@
       <c r="R103" s="5" t="inlineStr"/>
       <c r="S103" s="5" t="inlineStr"/>
       <c r="T103" s="5" t="inlineStr"/>
-      <c r="U103" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:95</t>
-        </is>
-      </c>
+      <c r="U103" s="5" t="inlineStr"/>
       <c r="V103" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,30；兑换 元能核心x1</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:107</t>
+        </is>
+      </c>
+      <c r="W103" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,30；兑换 秘制炸鸡桶x1</t>
         </is>
       </c>
     </row>
@@ -11097,23 +11254,24 @@
       <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
-      <c r="N104" s="5" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr"/>
+      <c r="O104" s="5" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="O104" s="5" t="inlineStr"/>
       <c r="P104" s="5" t="inlineStr"/>
       <c r="Q104" s="5" t="inlineStr"/>
       <c r="R104" s="5" t="inlineStr"/>
       <c r="S104" s="5" t="inlineStr"/>
       <c r="T104" s="5" t="inlineStr"/>
-      <c r="U104" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:96</t>
-        </is>
-      </c>
+      <c r="U104" s="5" t="inlineStr"/>
       <c r="V104" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:108</t>
+        </is>
+      </c>
+      <c r="W104" s="5" t="inlineStr">
         <is>
           <t>正式 ShopGoods.Price=19,10；兑换 猎鹰金币x100000</t>
         </is>
@@ -11146,13 +11304,13 @@
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="5" t="inlineStr"/>
-      <c r="K105" s="5" t="inlineStr">
+      <c r="K105" s="5" t="inlineStr"/>
+      <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr"/>
-      <c r="M105" s="5" t="inlineStr"/>
       <c r="N105" s="5" t="inlineStr"/>
       <c r="O105" s="5" t="inlineStr"/>
       <c r="P105" s="5" t="inlineStr"/>
@@ -11160,12 +11318,13 @@
       <c r="R105" s="5" t="inlineStr"/>
       <c r="S105" s="5" t="inlineStr"/>
       <c r="T105" s="5" t="inlineStr"/>
-      <c r="U105" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:97</t>
-        </is>
-      </c>
+      <c r="U105" s="5" t="inlineStr"/>
       <c r="V105" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:109</t>
+        </is>
+      </c>
+      <c r="W105" s="5" t="inlineStr">
         <is>
           <t>正式 ShopGoods.Price=19,10；兑换 高阶记录盘x10</t>
         </is>
@@ -11199,25 +11358,26 @@
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
       <c r="K106" s="5" t="inlineStr"/>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M106" s="5" t="inlineStr"/>
-      <c r="N106" s="5" t="inlineStr"/>
       <c r="O106" s="5" t="inlineStr"/>
       <c r="P106" s="5" t="inlineStr"/>
       <c r="Q106" s="5" t="inlineStr"/>
       <c r="R106" s="5" t="inlineStr"/>
       <c r="S106" s="5" t="inlineStr"/>
       <c r="T106" s="5" t="inlineStr"/>
-      <c r="U106" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:98</t>
-        </is>
-      </c>
+      <c r="U106" s="5" t="inlineStr"/>
       <c r="V106" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:110</t>
+        </is>
+      </c>
+      <c r="W106" s="5" t="inlineStr">
         <is>
           <t>正式 ShopGoods.Price=19,10；兑换 未知笔记x10</t>
         </is>
@@ -11226,7 +11386,7 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109006｜ShopId 1109</t>
+          <t>ShopGoods 1109007｜ShopId 1109</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -11236,7 +11396,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay50</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
@@ -11254,31 +11414,32 @@
       <c r="L107" s="5" t="inlineStr"/>
       <c r="M107" s="5" t="inlineStr"/>
       <c r="N107" s="5" t="inlineStr"/>
-      <c r="O107" s="5" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
+      <c r="O107" s="5" t="inlineStr"/>
       <c r="P107" s="5" t="inlineStr"/>
-      <c r="Q107" s="5" t="inlineStr"/>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="R107" s="5" t="inlineStr"/>
       <c r="S107" s="5" t="inlineStr"/>
       <c r="T107" s="5" t="inlineStr"/>
-      <c r="U107" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:99</t>
-        </is>
-      </c>
+      <c r="U107" s="5" t="inlineStr"/>
       <c r="V107" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,10；兑换 合淬喷剂x10000</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:112</t>
+        </is>
+      </c>
+      <c r="W107" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,10；兑换 校准元件x120</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109007｜ShopId 1109</t>
+          <t>ShopGoods 1109008｜ShopId 1109</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -11288,18 +11449,22 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay50</t>
+          <t>BuyLimit_Ever1</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I108" s="5" t="inlineStr"/>
       <c r="J108" s="5" t="inlineStr"/>
       <c r="K108" s="5" t="inlineStr"/>
@@ -11307,30 +11472,27 @@
       <c r="M108" s="5" t="inlineStr"/>
       <c r="N108" s="5" t="inlineStr"/>
       <c r="O108" s="5" t="inlineStr"/>
-      <c r="P108" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="P108" s="5" t="inlineStr"/>
       <c r="Q108" s="5" t="inlineStr"/>
       <c r="R108" s="5" t="inlineStr"/>
       <c r="S108" s="5" t="inlineStr"/>
       <c r="T108" s="5" t="inlineStr"/>
-      <c r="U108" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:100</t>
-        </is>
-      </c>
+      <c r="U108" s="5" t="inlineStr"/>
       <c r="V108" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,10；兑换 校准元件x120</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:113</t>
+        </is>
+      </c>
+      <c r="W108" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,1000；兑换 特供装置·单体x1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109008｜ShopId 1109</t>
+          <t>ShopGoods 1109009｜ShopId 1109</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -11346,17 +11508,17 @@
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
       <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" s="5" t="inlineStr"/>
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="5" t="inlineStr"/>
       <c r="K109" s="5" t="inlineStr"/>
       <c r="L109" s="5" t="inlineStr"/>
@@ -11368,21 +11530,22 @@
       <c r="R109" s="5" t="inlineStr"/>
       <c r="S109" s="5" t="inlineStr"/>
       <c r="T109" s="5" t="inlineStr"/>
-      <c r="U109" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:101</t>
-        </is>
-      </c>
+      <c r="U109" s="5" t="inlineStr"/>
       <c r="V109" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,500；兑换 特供装置·单体x1</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:114</t>
+        </is>
+      </c>
+      <c r="W109" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,2000；兑换 特供装置·范围x1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109009｜ShopId 1109</t>
+          <t>ShopGoods 1109010｜ShopId 1109</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -11392,25 +11555,25 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_Ever1</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr"/>
       <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J110" s="5" t="inlineStr"/>
-      <c r="K110" s="5" t="inlineStr"/>
       <c r="L110" s="5" t="inlineStr"/>
       <c r="M110" s="5" t="inlineStr"/>
       <c r="N110" s="5" t="inlineStr"/>
@@ -11420,45 +11583,42 @@
       <c r="R110" s="5" t="inlineStr"/>
       <c r="S110" s="5" t="inlineStr"/>
       <c r="T110" s="5" t="inlineStr"/>
-      <c r="U110" s="5" t="inlineStr">
-        <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena:102</t>
-        </is>
-      </c>
+      <c r="U110" s="5" t="inlineStr"/>
       <c r="V110" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,500；兑换 特供装置·范围x1</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:115</t>
+        </is>
+      </c>
+      <c r="W110" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,150；兑换 定轨组件x1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>ShopGoods 1109031｜ShopId 1109</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>单场胜利奖励</t>
+          <t>竞技场商店</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>每场胜利</t>
+          <t>BuyLimit_FourteenDay10</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="5" t="inlineStr"/>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="5" t="inlineStr"/>
@@ -11467,21 +11627,26 @@
       <c r="M111" s="5" t="inlineStr"/>
       <c r="N111" s="5" t="inlineStr"/>
       <c r="O111" s="5" t="inlineStr"/>
-      <c r="P111" s="5" t="inlineStr"/>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Q111" s="5" t="inlineStr"/>
       <c r="R111" s="5" t="inlineStr"/>
-      <c r="S111" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="S111" s="5" t="inlineStr"/>
       <c r="T111" s="5" t="inlineStr"/>
-      <c r="U111" s="5" t="inlineStr">
-        <is>
-          <t>竞技场:40</t>
-        </is>
-      </c>
-      <c r="V111" s="5" t="inlineStr"/>
+      <c r="U111" s="5" t="inlineStr"/>
+      <c r="V111" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena:116</t>
+        </is>
+      </c>
+      <c r="W111" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,15；兑换 收容凭证x1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -11491,24 +11656,24 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>单场失败奖励</t>
+          <t>单场胜利奖励</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>每场失败</t>
+          <t>每场胜利</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr"/>
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
@@ -11522,43 +11687,48 @@
       <c r="P112" s="5" t="inlineStr"/>
       <c r="Q112" s="5" t="inlineStr"/>
       <c r="R112" s="5" t="inlineStr"/>
-      <c r="S112" s="5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="T112" s="5" t="inlineStr"/>
-      <c r="U112" s="5" t="inlineStr">
-        <is>
-          <t>竞技场:44</t>
-        </is>
-      </c>
-      <c r="V112" s="5" t="inlineStr"/>
+      <c r="S112" s="5" t="inlineStr"/>
+      <c r="T112" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="U112" s="5" t="inlineStr"/>
+      <c r="V112" s="5" t="inlineStr">
+        <is>
+          <t>竞技场:40</t>
+        </is>
+      </c>
+      <c r="W112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>玩家等级1-10｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>正式单场胜利奖励引用</t>
+          <t>单场失败奖励</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>每场胜利</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>ArenaWinReward.DropId x26002001</t>
-        </is>
-      </c>
+          <t>每场失败</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr"/>
@@ -11571,18 +11741,23 @@
       <c r="Q113" s="5" t="inlineStr"/>
       <c r="R113" s="5" t="inlineStr"/>
       <c r="S113" s="5" t="inlineStr"/>
-      <c r="T113" s="5" t="inlineStr"/>
-      <c r="U113" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinReward.xlsx:5</t>
-        </is>
-      </c>
-      <c r="V113" s="5" t="inlineStr"/>
+      <c r="T113" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U113" s="5" t="inlineStr"/>
+      <c r="V113" s="5" t="inlineStr">
+        <is>
+          <t>竞技场:44</t>
+        </is>
+      </c>
+      <c r="W113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>玩家等级11-20｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>玩家等级1-10｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -11616,17 +11791,18 @@
       <c r="R114" s="5" t="inlineStr"/>
       <c r="S114" s="5" t="inlineStr"/>
       <c r="T114" s="5" t="inlineStr"/>
-      <c r="U114" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinReward.xlsx:6</t>
-        </is>
-      </c>
-      <c r="V114" s="5" t="inlineStr"/>
+      <c r="U114" s="5" t="inlineStr"/>
+      <c r="V114" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinReward.xlsx:5</t>
+        </is>
+      </c>
+      <c r="W114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>玩家等级21-30｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>玩家等级11-20｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -11660,17 +11836,18 @@
       <c r="R115" s="5" t="inlineStr"/>
       <c r="S115" s="5" t="inlineStr"/>
       <c r="T115" s="5" t="inlineStr"/>
-      <c r="U115" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinReward.xlsx:7</t>
-        </is>
-      </c>
-      <c r="V115" s="5" t="inlineStr"/>
+      <c r="U115" s="5" t="inlineStr"/>
+      <c r="V115" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinReward.xlsx:6</t>
+        </is>
+      </c>
+      <c r="W115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>玩家等级31-40｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>玩家等级21-30｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -11704,17 +11881,18 @@
       <c r="R116" s="5" t="inlineStr"/>
       <c r="S116" s="5" t="inlineStr"/>
       <c r="T116" s="5" t="inlineStr"/>
-      <c r="U116" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinReward.xlsx:8</t>
-        </is>
-      </c>
-      <c r="V116" s="5" t="inlineStr"/>
+      <c r="U116" s="5" t="inlineStr"/>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinReward.xlsx:7</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>玩家等级41-50｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>玩家等级31-40｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -11748,17 +11926,18 @@
       <c r="R117" s="5" t="inlineStr"/>
       <c r="S117" s="5" t="inlineStr"/>
       <c r="T117" s="5" t="inlineStr"/>
-      <c r="U117" s="5" t="inlineStr">
-        <is>
-          <t>正式:Arena/ArenaWinReward.xlsx:9</t>
-        </is>
-      </c>
-      <c r="V117" s="5" t="inlineStr"/>
+      <c r="U117" s="5" t="inlineStr"/>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinReward.xlsx:8</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>玩家等级51-60｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+          <t>玩家等级41-50｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -11792,15 +11971,61 @@
       <c r="R118" s="5" t="inlineStr"/>
       <c r="S118" s="5" t="inlineStr"/>
       <c r="T118" s="5" t="inlineStr"/>
-      <c r="U118" s="5" t="inlineStr">
+      <c r="U118" s="5" t="inlineStr"/>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>正式:Arena/ArenaWinReward.xlsx:9</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>玩家等级51-60｜每日免费刷新3次｜体力次数2次｜购买5次｜赛季14天</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>正式单场胜利奖励引用</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>每场胜利</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>ArenaWinReward.DropId x26002001</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr"/>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr"/>
+      <c r="K119" s="5" t="inlineStr"/>
+      <c r="L119" s="5" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr"/>
+      <c r="O119" s="5" t="inlineStr"/>
+      <c r="P119" s="5" t="inlineStr"/>
+      <c r="Q119" s="5" t="inlineStr"/>
+      <c r="R119" s="5" t="inlineStr"/>
+      <c r="S119" s="5" t="inlineStr"/>
+      <c r="T119" s="5" t="inlineStr"/>
+      <c r="U119" s="5" t="inlineStr"/>
+      <c r="V119" s="5" t="inlineStr">
         <is>
           <t>正式:Arena/ArenaWinReward.xlsx:10</t>
         </is>
       </c>
-      <c r="V118" s="5" t="inlineStr"/>
+      <c r="W119" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V118"/>
+  <autoFilter ref="A3:W119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -11814,7 +12039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11889,12 +12114,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>定轨组件</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -11939,12 +12164,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>合淬喷剂</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -11957,7 +12182,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -11989,12 +12214,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>未知笔记</t>
+          <t>校准元件</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -12007,7 +12232,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -12039,12 +12264,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>校准元件</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -12057,7 +12282,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -12089,12 +12314,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>特供装置·单体</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>96301</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -12139,12 +12364,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>特供装置·单体</t>
+          <t>特供装置·范围</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -12189,12 +12414,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>特供装置·范围</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -12599,11 +12824,11 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -12613,12 +12838,12 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>竞技场商店 x9</t>
+          <t>竞技场商店 x10</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>正式:Shop/ShopGoods.xlsx#Arena x9</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena x10</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -12857,8 +13082,58 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>抽卡/角色获取</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>收容凭证</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>竞技场商店</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>正式:Shop/ShopGoods.xlsx#Arena</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>周期/重复</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -12872,7 +13147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14733,7 +15008,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥5胜</t>
+          <t>赛季累胜≥3胜</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -14780,7 +15055,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>赛季累胜≥6胜</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -14827,7 +15102,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥9胜</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -14874,7 +15149,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥12胜</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -14921,7 +15196,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -14968,7 +15243,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥18胜</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -15015,7 +15290,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥24胜</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -15062,7 +15337,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥27胜</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -15109,7 +15384,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥60胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -15153,7 +15428,7 @@
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
@@ -15171,7 +15446,7 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
@@ -15180,7 +15455,7 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,500</t>
+          <t>正式 ShopGoods.Price=19,1000</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15476,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr"/>
@@ -15222,7 +15497,7 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
@@ -15261,7 +15536,7 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -15279,7 +15554,7 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
@@ -15288,7 +15563,7 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,500</t>
+          <t>正式 ShopGoods.Price=19,2000</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15584,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="5" t="inlineStr"/>
@@ -15330,7 +15605,7 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
@@ -15356,7 +15631,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -15369,16 +15644,16 @@
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109002｜ShopId 1109</t>
+          <t>ShopGoods 1109001｜ShopId 1109</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -15387,7 +15662,7 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -15396,7 +15671,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,30</t>
+          <t>正式 ShopGoods.Price=19,150</t>
         </is>
       </c>
     </row>
@@ -15417,19 +15692,19 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109002｜ShopId 1109</t>
+          <t>ShopGoods 1109001｜ShopId 1109</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -15438,7 +15713,7 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
@@ -15447,7 +15722,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>兑换 元能核心x1</t>
+          <t>兑换 熔晶x1</t>
         </is>
       </c>
     </row>
@@ -15464,11 +15739,11 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>高阶记录盘</t>
+          <t>定轨组件</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr">
@@ -15477,16 +15752,16 @@
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109004｜ShopId 1109</t>
+          <t>ShopGoods 1109010｜ShopId 1109</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -15495,7 +15770,7 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -15504,7 +15779,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,10</t>
+          <t>正式 ShopGoods.Price=19,150</t>
         </is>
       </c>
     </row>
@@ -15525,19 +15800,19 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay3</t>
+          <t>BuyLimit_FourteenDay1</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109004｜ShopId 1109</t>
+          <t>ShopGoods 1109010｜ShopId 1109</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -15546,7 +15821,7 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
@@ -15555,7 +15830,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>兑换 高阶记录盘x10</t>
+          <t>兑换 定轨组件x1</t>
         </is>
       </c>
     </row>
@@ -15572,11 +15847,11 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>未知笔记</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="5" t="inlineStr">
@@ -15585,7 +15860,7 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -15594,7 +15869,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109005｜ShopId 1109</t>
+          <t>ShopGoods 1109002｜ShopId 1109</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -15603,7 +15878,7 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
@@ -15612,7 +15887,7 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,10</t>
+          <t>正式 ShopGoods.Price=19,30</t>
         </is>
       </c>
     </row>
@@ -15633,7 +15908,7 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="5" t="inlineStr"/>
@@ -15645,7 +15920,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109005｜ShopId 1109</t>
+          <t>ShopGoods 1109002｜ShopId 1109</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -15654,7 +15929,7 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
@@ -15663,7 +15938,7 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>兑换 未知笔记x10</t>
+          <t>兑换 秘制炸鸡桶x1</t>
         </is>
       </c>
     </row>
@@ -15680,11 +15955,11 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>高阶记录盘</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="5" t="inlineStr">
@@ -15693,16 +15968,16 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109001｜ShopId 1109</t>
+          <t>ShopGoods 1109004｜ShopId 1109</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -15711,7 +15986,7 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
@@ -15720,7 +15995,7 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,150</t>
+          <t>正式 ShopGoods.Price=19,10</t>
         </is>
       </c>
     </row>
@@ -15741,19 +16016,19 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109001｜ShopId 1109</t>
+          <t>ShopGoods 1109004｜ShopId 1109</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -15762,7 +16037,7 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
@@ -15771,7 +16046,7 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>兑换 熔晶x1</t>
+          <t>兑换 高阶记录盘x10</t>
         </is>
       </c>
     </row>
@@ -15788,11 +16063,11 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>猎鹰金币</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>100000</v>
+        <v>10</v>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr">
@@ -15805,12 +16080,12 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109003｜ShopId 1109</t>
+          <t>ShopGoods 1109005｜ShopId 1109</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -15819,7 +16094,7 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
@@ -15856,12 +16131,12 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay5</t>
+          <t>BuyLimit_FourteenDay3</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109003｜ShopId 1109</t>
+          <t>ShopGoods 1109005｜ShopId 1109</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -15870,7 +16145,7 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
@@ -15879,7 +16154,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>兑换 猎鹰金币x100000</t>
+          <t>兑换 未知笔记x10</t>
         </is>
       </c>
     </row>
@@ -15896,11 +16171,11 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>合淬喷剂</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr">
@@ -15918,7 +16193,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109006｜ShopId 1109</t>
+          <t>ShopGoods 1109003｜ShopId 1109</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -15927,7 +16202,7 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
@@ -15969,7 +16244,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109006｜ShopId 1109</t>
+          <t>ShopGoods 1109003｜ShopId 1109</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -15978,7 +16253,7 @@
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
@@ -15987,7 +16262,7 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>兑换 合淬喷剂x10000</t>
+          <t>兑换 猎鹰金币x100000</t>
         </is>
       </c>
     </row>
@@ -16004,11 +16279,11 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>校准元件</t>
+          <t>收容凭证</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr">
@@ -16017,16 +16292,16 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay50</t>
+          <t>BuyLimit_FourteenDay10</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109007｜ShopId 1109</t>
+          <t>ShopGoods 1109031｜ShopId 1109</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -16035,7 +16310,7 @@
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
@@ -16044,7 +16319,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>正式 ShopGoods.Price=19,10</t>
+          <t>正式 ShopGoods.Price=19,15</t>
         </is>
       </c>
     </row>
@@ -16065,19 +16340,19 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>BuyLimit_FourteenDay50</t>
+          <t>BuyLimit_FourteenDay10</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>ShopGoods 1109007｜ShopId 1109</t>
+          <t>ShopGoods 1109031｜ShopId 1109</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -16086,7 +16361,7 @@
         </is>
       </c>
       <c r="K65" s="5" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
@@ -16095,14 +16370,14 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>兑换 校准元件x120</t>
+          <t>兑换 收容凭证x1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
+          <t>竞技场商店</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -16112,90 +16387,100 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>校准元件</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>勇士勋章</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>14天赛季</t>
+          <t>BuyLimit_FourteenDay50</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥5胜</t>
+          <t>ShopGoods 1109007｜ShopId 1109</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>直接奖励</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr"/>
+          <t>商店兑换商品</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>正式 ShopGoods.Price=19,10</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>产出</t>
+          <t>竞技场商店</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>消耗</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>勇士勋章</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>60</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>14天赛季</t>
+          <t>BuyLimit_FourteenDay50</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥10胜</t>
+          <t>ShopGoods 1109007｜ShopId 1109</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>配置页-竞技场</t>
+          <t>正式:Shop/ShopGoods.xlsx#Arena</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>直接奖励</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr"/>
+          <t>商店兑换货币</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>兑换 校准元件x120</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -16214,10 +16499,10 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
@@ -16228,7 +16513,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥15胜</t>
+          <t>赛季累胜≥5胜</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
@@ -16237,7 +16522,7 @@
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
@@ -16277,7 +16562,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥20胜</t>
+          <t>赛季累胜≥10胜</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -16286,7 +16571,7 @@
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
@@ -16308,14 +16593,14 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr"/>
@@ -16326,7 +16611,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥25胜</t>
+          <t>赛季累胜≥15胜</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
@@ -16335,7 +16620,7 @@
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
@@ -16361,10 +16646,10 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
       <c r="G71" s="5" t="inlineStr"/>
@@ -16375,7 +16660,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥30胜</t>
+          <t>赛季累胜≥20胜</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -16384,7 +16669,7 @@
         </is>
       </c>
       <c r="K71" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
@@ -16406,14 +16691,14 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr"/>
@@ -16424,7 +16709,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥40胜</t>
+          <t>赛季累胜≥25胜</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -16433,7 +16718,7 @@
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
@@ -16455,14 +16740,14 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr"/>
@@ -16473,7 +16758,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥50胜</t>
+          <t>赛季累胜≥30胜</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -16482,7 +16767,7 @@
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
@@ -16504,14 +16789,14 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr"/>
@@ -16522,7 +16807,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>赛季累胜≥60胜</t>
+          <t>赛季累胜≥40胜</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -16531,7 +16816,7 @@
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
@@ -16543,7 +16828,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -16557,10 +16842,10 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
       <c r="G75" s="5" t="inlineStr"/>
@@ -16571,7 +16856,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>达到传说｜积分≥3000</t>
+          <t>赛季累胜≥50胜</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -16580,7 +16865,7 @@
         </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
@@ -16592,7 +16877,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>赛季结算奖励</t>
+          <t>赛季累胜</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -16602,14 +16887,14 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>12000</v>
+        <v>400</v>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr"/>
@@ -16620,7 +16905,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>达到传说｜积分≥3000</t>
+          <t>赛季累胜≥60胜</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -16629,7 +16914,7 @@
         </is>
       </c>
       <c r="K76" s="5" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
@@ -16655,10 +16940,10 @@
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr"/>
@@ -16669,7 +16954,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅰ｜积分≥2900</t>
+          <t>达到传说｜积分≥3000</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -16678,7 +16963,7 @@
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
@@ -16704,10 +16989,10 @@
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>11500</v>
+        <v>12000</v>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr"/>
@@ -16718,7 +17003,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅰ｜积分≥2900</t>
+          <t>达到传说｜积分≥3000</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
@@ -16727,7 +17012,7 @@
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
@@ -16767,7 +17052,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅱ｜积分≥2800</t>
+          <t>达到大师Ⅰ｜积分≥2900</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -16776,7 +17061,7 @@
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
@@ -16802,10 +17087,10 @@
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>11000</v>
+        <v>11500</v>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
       <c r="G80" s="5" t="inlineStr"/>
@@ -16816,7 +17101,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅱ｜积分≥2800</t>
+          <t>达到大师Ⅰ｜积分≥2900</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
@@ -16825,7 +17110,7 @@
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
@@ -16865,7 +17150,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅲ｜积分≥2700</t>
+          <t>达到大师Ⅱ｜积分≥2800</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
@@ -16874,7 +17159,7 @@
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
@@ -16900,10 +17185,10 @@
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
       <c r="G82" s="5" t="inlineStr"/>
@@ -16914,7 +17199,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅲ｜积分≥2700</t>
+          <t>达到大师Ⅱ｜积分≥2800</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
@@ -16923,7 +17208,7 @@
         </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
@@ -16949,10 +17234,10 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
@@ -16963,7 +17248,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅰ｜积分≥1400</t>
+          <t>达到大师Ⅲ｜积分≥2700</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
@@ -16972,7 +17257,7 @@
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
@@ -16998,10 +17283,10 @@
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>400</v>
+        <v>1050</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4000</v>
+        <v>10500</v>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr"/>
@@ -17012,7 +17297,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅰ｜积分≥1400</t>
+          <t>达到大师Ⅲ｜积分≥2700</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
@@ -17021,7 +17306,7 @@
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
@@ -17061,7 +17346,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅱ｜积分≥1300</t>
+          <t>达到白银Ⅰ｜积分≥1400</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -17070,7 +17355,7 @@
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
@@ -17096,10 +17381,10 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr"/>
@@ -17110,7 +17395,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅱ｜积分≥1300</t>
+          <t>达到白银Ⅰ｜积分≥1400</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -17119,7 +17404,7 @@
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
@@ -17159,7 +17444,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅲ｜积分≥1200</t>
+          <t>达到白银Ⅱ｜积分≥1300</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -17168,7 +17453,7 @@
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
@@ -17194,10 +17479,10 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="inlineStr"/>
@@ -17208,7 +17493,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅲ｜积分≥1200</t>
+          <t>达到白银Ⅱ｜积分≥1300</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -17217,7 +17502,7 @@
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
@@ -17243,10 +17528,10 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr"/>
@@ -17257,7 +17542,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅰ｜积分≥2300</t>
+          <t>达到白银Ⅲ｜积分≥1200</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -17266,7 +17551,7 @@
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
@@ -17292,10 +17577,10 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>8500</v>
+        <v>3000</v>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr"/>
@@ -17306,7 +17591,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅰ｜积分≥2300</t>
+          <t>达到白银Ⅲ｜积分≥1200</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
@@ -17315,7 +17600,7 @@
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
@@ -17355,7 +17640,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅱ｜积分≥2200</t>
+          <t>达到翡翠Ⅰ｜积分≥2300</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
@@ -17364,7 +17649,7 @@
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
@@ -17390,10 +17675,10 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="inlineStr"/>
@@ -17404,7 +17689,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅱ｜积分≥2200</t>
+          <t>达到翡翠Ⅰ｜积分≥2300</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -17413,7 +17698,7 @@
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
@@ -17453,7 +17738,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅲ｜积分≥2100</t>
+          <t>达到翡翠Ⅱ｜积分≥2200</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -17462,7 +17747,7 @@
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
@@ -17488,10 +17773,10 @@
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr"/>
@@ -17502,7 +17787,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅲ｜积分≥2100</t>
+          <t>达到翡翠Ⅱ｜积分≥2200</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -17511,7 +17796,7 @@
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
@@ -17537,10 +17822,10 @@
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
       <c r="G95" s="5" t="inlineStr"/>
@@ -17551,7 +17836,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅰ｜积分≥2600</t>
+          <t>达到翡翠Ⅲ｜积分≥2100</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -17560,7 +17845,7 @@
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
@@ -17586,10 +17871,10 @@
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr"/>
@@ -17600,7 +17885,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅰ｜积分≥2600</t>
+          <t>达到翡翠Ⅲ｜积分≥2100</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -17609,7 +17894,7 @@
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
@@ -17649,7 +17934,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅱ｜积分≥2500</t>
+          <t>达到钻石Ⅰ｜积分≥2600</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -17658,7 +17943,7 @@
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
@@ -17684,10 +17969,10 @@
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
       <c r="G98" s="5" t="inlineStr"/>
@@ -17698,7 +17983,7 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅱ｜积分≥2500</t>
+          <t>达到钻石Ⅰ｜积分≥2600</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
@@ -17707,7 +17992,7 @@
         </is>
       </c>
       <c r="K98" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
@@ -17747,7 +18032,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅲ｜积分≥2400</t>
+          <t>达到钻石Ⅱ｜积分≥2500</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
@@ -17756,7 +18041,7 @@
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
@@ -17782,10 +18067,10 @@
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
@@ -17796,7 +18081,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅲ｜积分≥2400</t>
+          <t>达到钻石Ⅱ｜积分≥2500</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
@@ -17805,7 +18090,7 @@
         </is>
       </c>
       <c r="K100" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
@@ -17831,10 +18116,10 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
@@ -17845,7 +18130,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅰ｜积分≥2000</t>
+          <t>达到钻石Ⅲ｜积分≥2400</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -17854,7 +18139,7 @@
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
@@ -17880,10 +18165,10 @@
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
@@ -17894,7 +18179,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅰ｜积分≥2000</t>
+          <t>达到钻石Ⅲ｜积分≥2400</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
@@ -17903,7 +18188,7 @@
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
@@ -17943,7 +18228,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅱ｜积分≥1900</t>
+          <t>达到铂金Ⅰ｜积分≥2000</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
@@ -17952,7 +18237,7 @@
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
@@ -17978,10 +18263,10 @@
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>6500</v>
+        <v>7000</v>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr"/>
@@ -17992,7 +18277,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅱ｜积分≥1900</t>
+          <t>达到铂金Ⅰ｜积分≥2000</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -18001,7 +18286,7 @@
         </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
@@ -18041,7 +18326,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅲ｜积分≥1800</t>
+          <t>达到铂金Ⅱ｜积分≥1900</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
@@ -18050,7 +18335,7 @@
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
@@ -18076,10 +18361,10 @@
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
@@ -18090,7 +18375,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅲ｜积分≥1800</t>
+          <t>达到铂金Ⅱ｜积分≥1900</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
@@ -18099,7 +18384,7 @@
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
@@ -18125,10 +18410,10 @@
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
       <c r="G107" s="5" t="inlineStr"/>
@@ -18139,7 +18424,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅰ｜积分≥1100</t>
+          <t>达到铂金Ⅲ｜积分≥1800</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
@@ -18148,7 +18433,7 @@
         </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
@@ -18174,10 +18459,10 @@
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr"/>
@@ -18188,7 +18473,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅰ｜积分≥1100</t>
+          <t>达到铂金Ⅲ｜积分≥1800</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
@@ -18197,7 +18482,7 @@
         </is>
       </c>
       <c r="K108" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
@@ -18237,7 +18522,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅱ｜积分≥1000</t>
+          <t>达到青铜Ⅰ｜积分≥1100</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
@@ -18246,7 +18531,7 @@
         </is>
       </c>
       <c r="K109" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
@@ -18272,10 +18557,10 @@
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr"/>
@@ -18286,7 +18571,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅱ｜积分≥1000</t>
+          <t>达到青铜Ⅰ｜积分≥1100</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
@@ -18295,7 +18580,7 @@
         </is>
       </c>
       <c r="K110" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
@@ -18335,7 +18620,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅲ｜积分≥0</t>
+          <t>达到青铜Ⅱ｜积分≥1000</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -18344,7 +18629,7 @@
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
@@ -18370,10 +18655,10 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr"/>
@@ -18384,7 +18669,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅲ｜积分≥0</t>
+          <t>达到青铜Ⅱ｜积分≥1000</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
@@ -18393,7 +18678,7 @@
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
@@ -18419,10 +18704,10 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr"/>
@@ -18433,7 +18718,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅰ｜积分≥1700</t>
+          <t>达到青铜Ⅲ｜积分≥0</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
@@ -18442,7 +18727,7 @@
         </is>
       </c>
       <c r="K113" s="5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
@@ -18468,10 +18753,10 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr"/>
@@ -18482,7 +18767,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅰ｜积分≥1700</t>
+          <t>达到青铜Ⅲ｜积分≥0</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
@@ -18491,7 +18776,7 @@
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
@@ -18531,7 +18816,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅱ｜积分≥1600</t>
+          <t>达到黄金Ⅰ｜积分≥1700</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
@@ -18540,7 +18825,7 @@
         </is>
       </c>
       <c r="K115" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
@@ -18566,10 +18851,10 @@
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
@@ -18580,7 +18865,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅱ｜积分≥1600</t>
+          <t>达到黄金Ⅰ｜积分≥1700</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -18589,7 +18874,7 @@
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
@@ -18629,7 +18914,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅲ｜积分≥1500</t>
+          <t>达到黄金Ⅱ｜积分≥1600</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
@@ -18638,7 +18923,7 @@
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
@@ -18664,10 +18949,10 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
@@ -18678,7 +18963,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅲ｜积分≥1500</t>
+          <t>达到黄金Ⅱ｜积分≥1600</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -18687,7 +18972,7 @@
         </is>
       </c>
       <c r="K118" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
@@ -18699,7 +18984,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励</t>
+          <t>赛季结算奖励</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -18713,21 +18998,21 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>生涯一次性</t>
+          <t>14天赛季</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>达到传说｜积分≥3000</t>
+          <t>达到黄金Ⅲ｜积分≥1500</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -18736,7 +19021,7 @@
         </is>
       </c>
       <c r="K119" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
@@ -18748,7 +19033,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>首次到达奖励</t>
+          <t>赛季结算奖励</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -18762,21 +19047,21 @@
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>生涯一次性</t>
+          <t>14天赛季</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅰ｜积分≥2900</t>
+          <t>达到黄金Ⅲ｜积分≥1500</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
@@ -18785,7 +19070,7 @@
         </is>
       </c>
       <c r="K120" s="5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
@@ -18807,14 +19092,14 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
@@ -18825,7 +19110,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅱ｜积分≥2800</t>
+          <t>达到传说｜积分≥3000</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -18834,7 +19119,7 @@
         </is>
       </c>
       <c r="K121" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
@@ -18856,14 +19141,14 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
@@ -18874,7 +19159,7 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>达到大师Ⅲ｜积分≥2700</t>
+          <t>达到大师Ⅰ｜积分≥2900</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
@@ -18883,7 +19168,7 @@
         </is>
       </c>
       <c r="K122" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
@@ -18905,14 +19190,14 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
       <c r="G123" s="5" t="inlineStr"/>
@@ -18923,7 +19208,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅰ｜积分≥1400</t>
+          <t>达到大师Ⅱ｜积分≥2800</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -18932,7 +19217,7 @@
         </is>
       </c>
       <c r="K123" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
@@ -18954,14 +19239,14 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F124" s="5" t="inlineStr"/>
       <c r="G124" s="5" t="inlineStr"/>
@@ -18972,7 +19257,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅱ｜积分≥1300</t>
+          <t>达到大师Ⅲ｜积分≥2700</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
@@ -18981,7 +19266,7 @@
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
@@ -19003,14 +19288,14 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
         <v>600</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr"/>
@@ -19021,7 +19306,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>达到白银Ⅲ｜积分≥1200</t>
+          <t>达到白银Ⅰ｜积分≥1400</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -19030,7 +19315,7 @@
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
@@ -19052,14 +19337,14 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>8000</v>
+        <v>600</v>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr"/>
@@ -19070,7 +19355,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅰ｜积分≥2300</t>
+          <t>达到白银Ⅱ｜积分≥1300</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
@@ -19079,7 +19364,7 @@
         </is>
       </c>
       <c r="K126" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
@@ -19101,14 +19386,14 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
@@ -19119,7 +19404,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅱ｜积分≥2200</t>
+          <t>达到白银Ⅲ｜积分≥1200</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -19128,7 +19413,7 @@
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
@@ -19150,14 +19435,14 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
         <v>800</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr"/>
@@ -19168,7 +19453,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>达到翡翠Ⅲ｜积分≥2100</t>
+          <t>达到翡翠Ⅰ｜积分≥2300</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -19177,7 +19462,7 @@
         </is>
       </c>
       <c r="K128" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
@@ -19199,14 +19484,14 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>10000</v>
+        <v>800</v>
       </c>
       <c r="F129" s="5" t="inlineStr"/>
       <c r="G129" s="5" t="inlineStr"/>
@@ -19217,7 +19502,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅰ｜积分≥2600</t>
+          <t>达到翡翠Ⅱ｜积分≥2200</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -19226,7 +19511,7 @@
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
@@ -19248,14 +19533,14 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
@@ -19266,7 +19551,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅱ｜积分≥2500</t>
+          <t>达到翡翠Ⅲ｜积分≥2100</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
@@ -19275,7 +19560,7 @@
         </is>
       </c>
       <c r="K130" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
@@ -19297,14 +19582,14 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
       <c r="G131" s="5" t="inlineStr"/>
@@ -19315,7 +19600,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>达到钻石Ⅲ｜积分≥2400</t>
+          <t>达到钻石Ⅰ｜积分≥2600</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
@@ -19324,7 +19609,7 @@
         </is>
       </c>
       <c r="K131" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
@@ -19346,14 +19631,14 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="F132" s="5" t="inlineStr"/>
       <c r="G132" s="5" t="inlineStr"/>
@@ -19364,7 +19649,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅰ｜积分≥2000</t>
+          <t>达到钻石Ⅱ｜积分≥2500</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
@@ -19373,7 +19658,7 @@
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
@@ -19395,14 +19680,14 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
       <c r="G133" s="5" t="inlineStr"/>
@@ -19413,7 +19698,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅱ｜积分≥1900</t>
+          <t>达到钻石Ⅲ｜积分≥2400</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -19422,7 +19707,7 @@
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
@@ -19444,14 +19729,14 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
         <v>800</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="F134" s="5" t="inlineStr"/>
       <c r="G134" s="5" t="inlineStr"/>
@@ -19462,7 +19747,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>达到铂金Ⅲ｜积分≥1800</t>
+          <t>达到铂金Ⅰ｜积分≥2000</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
@@ -19471,7 +19756,7 @@
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
@@ -19493,14 +19778,14 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>竞技场代币</t>
+          <t>炮台升级小材料</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="F135" s="5" t="inlineStr"/>
       <c r="G135" s="5" t="inlineStr"/>
@@ -19511,7 +19796,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅰ｜积分≥1100</t>
+          <t>达到铂金Ⅱ｜积分≥1900</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
@@ -19520,7 +19805,7 @@
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
@@ -19542,14 +19827,14 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>B炮台</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
       <c r="G136" s="5" t="inlineStr"/>
@@ -19560,7 +19845,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>达到青铜Ⅱ｜积分≥1000</t>
+          <t>达到铂金Ⅲ｜积分≥1800</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -19569,7 +19854,7 @@
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
@@ -19595,10 +19880,10 @@
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="F137" s="5" t="inlineStr"/>
       <c r="G137" s="5" t="inlineStr"/>
@@ -19609,7 +19894,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅰ｜积分≥1700</t>
+          <t>达到青铜Ⅰ｜积分≥1100</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
@@ -19618,7 +19903,7 @@
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
@@ -19640,14 +19925,14 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>炮台升级小材料</t>
+          <t>B炮台</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F138" s="5" t="inlineStr"/>
       <c r="G138" s="5" t="inlineStr"/>
@@ -19658,7 +19943,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>达到黄金Ⅱ｜积分≥1600</t>
+          <t>达到青铜Ⅱ｜积分≥1000</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
@@ -19667,7 +19952,7 @@
         </is>
       </c>
       <c r="K138" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
@@ -19689,14 +19974,14 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>竞技场代币</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
         <v>600</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="F139" s="5" t="inlineStr"/>
       <c r="G139" s="5" t="inlineStr"/>
@@ -19707,26 +19992,124 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
+          <t>达到黄金Ⅰ｜积分≥1700</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>直接奖励</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>首次到达奖励</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>炮台升级小材料</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>生涯一次性</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>达到黄金Ⅱ｜积分≥1600</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>配置页-竞技场</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>直接奖励</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>首次到达奖励</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>生涯一次性</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
           <t>达到黄金Ⅲ｜积分≥1500</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
+      <c r="J141" s="5" t="inlineStr">
         <is>
           <t>配置页-竞技场</t>
         </is>
       </c>
-      <c r="K139" s="5" t="n">
+      <c r="K141" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L139" s="5" t="inlineStr">
+      <c r="L141" s="5" t="inlineStr">
         <is>
           <t>直接奖励</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr"/>
+      <c r="M141" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M139"/>
+  <autoFilter ref="A1:M141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
